--- a/SpaceDebris_site_1000/2007-048IA_Blok-I_Soyuz-FG_Fregat.xlsx
+++ b/SpaceDebris_site_1000/2007-048IA_Blok-I_Soyuz-FG_Fregat.xlsx
@@ -452,7002 +452,7002 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107.98</v>
+        <v>0.19</v>
       </c>
       <c r="B2" t="n">
-        <v>37483</v>
+        <v>37522</v>
       </c>
       <c r="C2" t="n">
-        <v>111.4</v>
+        <v>4.66</v>
       </c>
       <c r="D2" t="n">
-        <v>25362</v>
+        <v>18873</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106.7</v>
+        <v>0.74</v>
       </c>
       <c r="B3" t="n">
-        <v>42286</v>
+        <v>36474</v>
       </c>
       <c r="C3" t="n">
-        <v>108.85</v>
+        <v>10.21</v>
       </c>
       <c r="D3" t="n">
-        <v>20617</v>
+        <v>16610</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>92.02</v>
+        <v>1.14</v>
       </c>
       <c r="B4" t="n">
-        <v>28602</v>
+        <v>37078</v>
       </c>
       <c r="C4" t="n">
-        <v>90.28</v>
+        <v>2.13</v>
       </c>
       <c r="D4" t="n">
-        <v>22330</v>
+        <v>19646</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>42.48</v>
+        <v>1.31</v>
       </c>
       <c r="B5" t="n">
-        <v>23211</v>
+        <v>36890</v>
       </c>
       <c r="C5" t="n">
-        <v>42</v>
+        <v>3.4</v>
       </c>
       <c r="D5" t="n">
-        <v>17261</v>
+        <v>23898</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104.96</v>
+        <v>1.54</v>
       </c>
       <c r="B6" t="n">
-        <v>45572</v>
+        <v>38692</v>
       </c>
       <c r="C6" t="n">
-        <v>107.11</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>25752</v>
+        <v>29346</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107.1</v>
+        <v>1.65</v>
       </c>
       <c r="B7" t="n">
-        <v>41606</v>
+        <v>36242</v>
       </c>
       <c r="C7" t="n">
-        <v>107.62</v>
+        <v>0.17</v>
       </c>
       <c r="D7" t="n">
-        <v>10383</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>169.18</v>
+        <v>2.15</v>
       </c>
       <c r="B8" t="n">
-        <v>24579</v>
+        <v>37219</v>
       </c>
       <c r="C8" t="n">
-        <v>170.07</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>12718</v>
+        <v>17063</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110.54</v>
+        <v>3</v>
       </c>
       <c r="B9" t="n">
-        <v>31771</v>
+        <v>34945</v>
       </c>
       <c r="C9" t="n">
-        <v>107.44</v>
+        <v>5.03</v>
       </c>
       <c r="D9" t="n">
-        <v>22236</v>
+        <v>23735</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112.1</v>
+        <v>4.03</v>
       </c>
       <c r="B10" t="n">
-        <v>26455</v>
+        <v>34937</v>
       </c>
       <c r="C10" t="n">
-        <v>115.37</v>
+        <v>4.74</v>
       </c>
       <c r="D10" t="n">
-        <v>22078</v>
+        <v>21035</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95.58</v>
+        <v>4.13</v>
       </c>
       <c r="B11" t="n">
-        <v>35723</v>
+        <v>37141</v>
       </c>
       <c r="C11" t="n">
-        <v>96.73999999999999</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>28114</v>
+        <v>14105</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>140.19</v>
+        <v>5.18</v>
       </c>
       <c r="B12" t="n">
-        <v>23505</v>
+        <v>35559</v>
       </c>
       <c r="C12" t="n">
-        <v>143.37</v>
+        <v>9.25</v>
       </c>
       <c r="D12" t="n">
-        <v>17571</v>
+        <v>13722</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>93.98</v>
+        <v>6.15</v>
       </c>
       <c r="B13" t="n">
-        <v>32233</v>
+        <v>34350</v>
       </c>
       <c r="C13" t="n">
-        <v>90.36</v>
+        <v>1.07</v>
       </c>
       <c r="D13" t="n">
-        <v>11795</v>
+        <v>21508</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>91.59</v>
+        <v>6.64</v>
       </c>
       <c r="B14" t="n">
-        <v>24822</v>
+        <v>32572</v>
       </c>
       <c r="C14" t="n">
-        <v>94.28</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>19809</v>
+        <v>28555</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>173.17</v>
+        <v>7.01</v>
       </c>
       <c r="B15" t="n">
-        <v>23714</v>
+        <v>32665</v>
       </c>
       <c r="C15" t="n">
-        <v>170.28</v>
+        <v>11.43</v>
       </c>
       <c r="D15" t="n">
-        <v>16937</v>
+        <v>12127</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112.35</v>
+        <v>7.06</v>
       </c>
       <c r="B16" t="n">
-        <v>25550</v>
+        <v>33681</v>
       </c>
       <c r="C16" t="n">
-        <v>114.19</v>
+        <v>1.96</v>
       </c>
       <c r="D16" t="n">
-        <v>10812</v>
+        <v>20873</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>101.72</v>
+        <v>7.78</v>
       </c>
       <c r="B17" t="n">
-        <v>46392</v>
+        <v>32331</v>
       </c>
       <c r="C17" t="n">
-        <v>100.85</v>
+        <v>13.41</v>
       </c>
       <c r="D17" t="n">
-        <v>11187</v>
+        <v>21197</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104.08</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="B18" t="n">
-        <v>45621</v>
+        <v>31820</v>
       </c>
       <c r="C18" t="n">
-        <v>107.69</v>
+        <v>8.48</v>
       </c>
       <c r="D18" t="n">
-        <v>11448</v>
+        <v>22549</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114.48</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="B19" t="n">
-        <v>24455</v>
+        <v>30876</v>
       </c>
       <c r="C19" t="n">
-        <v>116.47</v>
+        <v>11.3</v>
       </c>
       <c r="D19" t="n">
-        <v>19769</v>
+        <v>29339</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>91.77</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="B20" t="n">
-        <v>25099</v>
+        <v>32875</v>
       </c>
       <c r="C20" t="n">
-        <v>94.59</v>
+        <v>20.1</v>
       </c>
       <c r="D20" t="n">
-        <v>20487</v>
+        <v>24852</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>100.34</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="B21" t="n">
-        <v>45217</v>
+        <v>33060</v>
       </c>
       <c r="C21" t="n">
-        <v>97.23999999999999</v>
+        <v>12.23</v>
       </c>
       <c r="D21" t="n">
-        <v>16240</v>
+        <v>16144</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>106.11</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="B22" t="n">
-        <v>47265</v>
+        <v>32500</v>
       </c>
       <c r="C22" t="n">
-        <v>102.05</v>
+        <v>6.33</v>
       </c>
       <c r="D22" t="n">
-        <v>14016</v>
+        <v>28764</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109.64</v>
+        <v>9.66</v>
       </c>
       <c r="B23" t="n">
-        <v>35322</v>
+        <v>31426</v>
       </c>
       <c r="C23" t="n">
-        <v>107.95</v>
+        <v>11.11</v>
       </c>
       <c r="D23" t="n">
-        <v>25809</v>
+        <v>14782</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>61.84</v>
+        <v>9.66</v>
       </c>
       <c r="B24" t="n">
-        <v>20456</v>
+        <v>31552</v>
       </c>
       <c r="C24" t="n">
-        <v>61.7</v>
+        <v>11.27</v>
       </c>
       <c r="D24" t="n">
-        <v>21405</v>
+        <v>24545</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104.85</v>
+        <v>9.9</v>
       </c>
       <c r="B25" t="n">
-        <v>47592</v>
+        <v>30523</v>
       </c>
       <c r="C25" t="n">
-        <v>108.99</v>
+        <v>16.09</v>
       </c>
       <c r="D25" t="n">
-        <v>14813</v>
+        <v>19658</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>90.91</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="B26" t="n">
-        <v>21599</v>
+        <v>31427</v>
       </c>
       <c r="C26" t="n">
-        <v>91.23999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="D26" t="n">
-        <v>21565</v>
+        <v>10148</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>84.14</v>
+        <v>10</v>
       </c>
       <c r="B27" t="n">
-        <v>21217</v>
+        <v>28325</v>
       </c>
       <c r="C27" t="n">
-        <v>84.94</v>
+        <v>10.14</v>
       </c>
       <c r="D27" t="n">
-        <v>28834</v>
+        <v>13939</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>17.04</v>
+        <v>10.25</v>
       </c>
       <c r="B28" t="n">
-        <v>22134</v>
+        <v>29901</v>
       </c>
       <c r="C28" t="n">
-        <v>16.41</v>
+        <v>10.88</v>
       </c>
       <c r="D28" t="n">
-        <v>18044</v>
+        <v>21692</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104.77</v>
+        <v>11.12</v>
       </c>
       <c r="B29" t="n">
-        <v>43923</v>
+        <v>27579</v>
       </c>
       <c r="C29" t="n">
-        <v>100.33</v>
+        <v>16.33</v>
       </c>
       <c r="D29" t="n">
-        <v>17819</v>
+        <v>17404</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>102.41</v>
+        <v>11.34</v>
       </c>
       <c r="B30" t="n">
-        <v>49090</v>
+        <v>29481</v>
       </c>
       <c r="C30" t="n">
-        <v>100.83</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>10098</v>
+        <v>22158</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109.06</v>
+        <v>11.37</v>
       </c>
       <c r="B31" t="n">
-        <v>34554</v>
+        <v>26902</v>
       </c>
       <c r="C31" t="n">
-        <v>109.2</v>
+        <v>11.79</v>
       </c>
       <c r="D31" t="n">
-        <v>10815</v>
+        <v>12969</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>8.960000000000001</v>
+        <v>12.52</v>
       </c>
       <c r="B32" t="n">
-        <v>25250</v>
+        <v>26323</v>
       </c>
       <c r="C32" t="n">
-        <v>9.01</v>
+        <v>9.23</v>
       </c>
       <c r="D32" t="n">
-        <v>28481</v>
+        <v>27394</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>94.17</v>
+        <v>12.99</v>
       </c>
       <c r="B33" t="n">
-        <v>31139</v>
+        <v>30086</v>
       </c>
       <c r="C33" t="n">
-        <v>95.51000000000001</v>
+        <v>10.04</v>
       </c>
       <c r="D33" t="n">
-        <v>14136</v>
+        <v>18992</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>108.27</v>
+        <v>13.25</v>
       </c>
       <c r="B34" t="n">
-        <v>37122</v>
+        <v>28453</v>
       </c>
       <c r="C34" t="n">
-        <v>112.22</v>
+        <v>21.69</v>
       </c>
       <c r="D34" t="n">
-        <v>28240</v>
+        <v>12290</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>94.43000000000001</v>
+        <v>13.94</v>
       </c>
       <c r="B35" t="n">
-        <v>31825</v>
+        <v>26539</v>
       </c>
       <c r="C35" t="n">
-        <v>97.12</v>
+        <v>13.17</v>
       </c>
       <c r="D35" t="n">
-        <v>21435</v>
+        <v>16254</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>91.23999999999999</v>
+        <v>14.37</v>
       </c>
       <c r="B36" t="n">
-        <v>25393</v>
+        <v>26308</v>
       </c>
       <c r="C36" t="n">
-        <v>92.59999999999999</v>
+        <v>14.87</v>
       </c>
       <c r="D36" t="n">
-        <v>18168</v>
+        <v>10722</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>99.97</v>
+        <v>14.48</v>
       </c>
       <c r="B37" t="n">
-        <v>45664</v>
+        <v>27677</v>
       </c>
       <c r="C37" t="n">
-        <v>97.41</v>
+        <v>9.57</v>
       </c>
       <c r="D37" t="n">
-        <v>13130</v>
+        <v>10517</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>93.27</v>
+        <v>15.74</v>
       </c>
       <c r="B38" t="n">
-        <v>30507</v>
+        <v>26822</v>
       </c>
       <c r="C38" t="n">
-        <v>91.34999999999999</v>
+        <v>18.14</v>
       </c>
       <c r="D38" t="n">
-        <v>21676</v>
+        <v>22026</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>101.9</v>
+        <v>15.9</v>
       </c>
       <c r="B39" t="n">
-        <v>48950</v>
+        <v>27084</v>
       </c>
       <c r="C39" t="n">
-        <v>99.04000000000001</v>
+        <v>15.9</v>
       </c>
       <c r="D39" t="n">
-        <v>12612</v>
+        <v>12541</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>92.43000000000001</v>
+        <v>16.03</v>
       </c>
       <c r="B40" t="n">
-        <v>27670</v>
+        <v>23958</v>
       </c>
       <c r="C40" t="n">
-        <v>88.54000000000001</v>
+        <v>19.33</v>
       </c>
       <c r="D40" t="n">
-        <v>14761</v>
+        <v>26072</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>83.03</v>
+        <v>16.35</v>
       </c>
       <c r="B41" t="n">
-        <v>24763</v>
+        <v>26956</v>
       </c>
       <c r="C41" t="n">
-        <v>83.40000000000001</v>
+        <v>18.26</v>
       </c>
       <c r="D41" t="n">
-        <v>11036</v>
+        <v>28921</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133.54</v>
+        <v>16.43</v>
       </c>
       <c r="B42" t="n">
-        <v>24622</v>
+        <v>26518</v>
       </c>
       <c r="C42" t="n">
-        <v>136.08</v>
+        <v>23.71</v>
       </c>
       <c r="D42" t="n">
-        <v>26648</v>
+        <v>13112</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>98.65000000000001</v>
+        <v>16.66</v>
       </c>
       <c r="B43" t="n">
-        <v>43500</v>
+        <v>25376</v>
       </c>
       <c r="C43" t="n">
-        <v>101.85</v>
+        <v>23.76</v>
       </c>
       <c r="D43" t="n">
-        <v>22851</v>
+        <v>11535</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>99.75</v>
+        <v>17.34</v>
       </c>
       <c r="B44" t="n">
-        <v>44106</v>
+        <v>23370</v>
       </c>
       <c r="C44" t="n">
-        <v>98.06</v>
+        <v>21</v>
       </c>
       <c r="D44" t="n">
-        <v>21644</v>
+        <v>26877</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>96.8</v>
+        <v>17.89</v>
       </c>
       <c r="B45" t="n">
-        <v>39715</v>
+        <v>25477</v>
       </c>
       <c r="C45" t="n">
-        <v>93.81999999999999</v>
+        <v>17.92</v>
       </c>
       <c r="D45" t="n">
-        <v>10598</v>
+        <v>11997</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>108.14</v>
+        <v>17.99</v>
       </c>
       <c r="B46" t="n">
-        <v>37451</v>
+        <v>22701</v>
       </c>
       <c r="C46" t="n">
-        <v>109.33</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>13571</v>
+        <v>18328</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>114.94</v>
+        <v>18.01</v>
       </c>
       <c r="B47" t="n">
-        <v>24258</v>
+        <v>24825</v>
       </c>
       <c r="C47" t="n">
-        <v>117.52</v>
+        <v>22.25</v>
       </c>
       <c r="D47" t="n">
-        <v>18380</v>
+        <v>28740</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>90.36</v>
+        <v>18.59</v>
       </c>
       <c r="B48" t="n">
-        <v>23705</v>
+        <v>25418</v>
       </c>
       <c r="C48" t="n">
-        <v>88.05</v>
+        <v>19.54</v>
       </c>
       <c r="D48" t="n">
-        <v>15303</v>
+        <v>29459</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>94.48</v>
+        <v>19.1</v>
       </c>
       <c r="B49" t="n">
-        <v>33718</v>
+        <v>21263</v>
       </c>
       <c r="C49" t="n">
-        <v>97.18000000000001</v>
+        <v>18.83</v>
       </c>
       <c r="D49" t="n">
-        <v>22227</v>
+        <v>12954</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>92.16</v>
+        <v>19.25</v>
       </c>
       <c r="B50" t="n">
-        <v>25082</v>
+        <v>22615</v>
       </c>
       <c r="C50" t="n">
-        <v>95.98999999999999</v>
+        <v>19.18</v>
       </c>
       <c r="D50" t="n">
-        <v>14958</v>
+        <v>19325</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>106.76</v>
+        <v>19.71</v>
       </c>
       <c r="B51" t="n">
-        <v>41234</v>
+        <v>24223</v>
       </c>
       <c r="C51" t="n">
-        <v>104.89</v>
+        <v>11.69</v>
       </c>
       <c r="D51" t="n">
-        <v>16794</v>
+        <v>27158</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>114.03</v>
+        <v>20.02</v>
       </c>
       <c r="B52" t="n">
-        <v>23549</v>
+        <v>21304</v>
       </c>
       <c r="C52" t="n">
-        <v>111.84</v>
+        <v>23.89</v>
       </c>
       <c r="D52" t="n">
-        <v>12517</v>
+        <v>17096</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>37.37</v>
+        <v>20.77</v>
       </c>
       <c r="B53" t="n">
-        <v>25121</v>
+        <v>21004</v>
       </c>
       <c r="C53" t="n">
-        <v>36.16</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>25075</v>
+        <v>15880</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>114.22</v>
+        <v>20.85</v>
       </c>
       <c r="B54" t="n">
-        <v>26112</v>
+        <v>23662</v>
       </c>
       <c r="C54" t="n">
-        <v>118.22</v>
+        <v>14.51</v>
       </c>
       <c r="D54" t="n">
-        <v>13492</v>
+        <v>11817</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>99.61</v>
+        <v>20.91</v>
       </c>
       <c r="B55" t="n">
-        <v>45646</v>
+        <v>23451</v>
       </c>
       <c r="C55" t="n">
-        <v>101.1</v>
+        <v>25.62</v>
       </c>
       <c r="D55" t="n">
-        <v>28361</v>
+        <v>23392</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>20.74</v>
+        <v>21.27</v>
       </c>
       <c r="B56" t="n">
-        <v>24590</v>
+        <v>24099</v>
       </c>
       <c r="C56" t="n">
-        <v>21.87</v>
+        <v>27.91</v>
       </c>
       <c r="D56" t="n">
-        <v>20356</v>
+        <v>28365</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>102.73</v>
+        <v>21.66</v>
       </c>
       <c r="B57" t="n">
-        <v>47113</v>
+        <v>23779</v>
       </c>
       <c r="C57" t="n">
-        <v>102.92</v>
+        <v>20.43</v>
       </c>
       <c r="D57" t="n">
-        <v>12575</v>
+        <v>25927</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137.25</v>
+        <v>21.75</v>
       </c>
       <c r="B58" t="n">
-        <v>23056</v>
+        <v>22538</v>
       </c>
       <c r="C58" t="n">
-        <v>139.12</v>
+        <v>19.96</v>
       </c>
       <c r="D58" t="n">
-        <v>12270</v>
+        <v>15922</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>93.3</v>
+        <v>21.88</v>
       </c>
       <c r="B59" t="n">
-        <v>29525</v>
+        <v>24907</v>
       </c>
       <c r="C59" t="n">
-        <v>96.42</v>
+        <v>12.21</v>
       </c>
       <c r="D59" t="n">
-        <v>24497</v>
+        <v>22412</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>93.65000000000001</v>
+        <v>22.15</v>
       </c>
       <c r="B60" t="n">
-        <v>31240</v>
+        <v>23024</v>
       </c>
       <c r="C60" t="n">
-        <v>94.18000000000001</v>
+        <v>21.96</v>
       </c>
       <c r="D60" t="n">
-        <v>29521</v>
+        <v>22756</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>105.42</v>
+        <v>22.32</v>
       </c>
       <c r="B61" t="n">
-        <v>43282</v>
+        <v>20772</v>
       </c>
       <c r="C61" t="n">
-        <v>104.5</v>
+        <v>18.95</v>
       </c>
       <c r="D61" t="n">
-        <v>19660</v>
+        <v>19503</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>174.29</v>
+        <v>22.8</v>
       </c>
       <c r="B62" t="n">
-        <v>22258</v>
+        <v>24869</v>
       </c>
       <c r="C62" t="n">
-        <v>168.41</v>
+        <v>30.16</v>
       </c>
       <c r="D62" t="n">
-        <v>27882</v>
+        <v>20524</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>106.38</v>
+        <v>22.9</v>
       </c>
       <c r="B63" t="n">
-        <v>43327</v>
+        <v>22516</v>
       </c>
       <c r="C63" t="n">
-        <v>104.1</v>
+        <v>19.81</v>
       </c>
       <c r="D63" t="n">
-        <v>21938</v>
+        <v>20930</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>92.53</v>
+        <v>23.24</v>
       </c>
       <c r="B64" t="n">
-        <v>27247</v>
+        <v>23512</v>
       </c>
       <c r="C64" t="n">
-        <v>90.08</v>
+        <v>23.2</v>
       </c>
       <c r="D64" t="n">
-        <v>11747</v>
+        <v>12837</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>94.55</v>
+        <v>23.84</v>
       </c>
       <c r="B65" t="n">
-        <v>31524</v>
+        <v>24729</v>
       </c>
       <c r="C65" t="n">
-        <v>94.02</v>
+        <v>21.69</v>
       </c>
       <c r="D65" t="n">
-        <v>20797</v>
+        <v>27702</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>14.88</v>
+        <v>24.54</v>
       </c>
       <c r="B66" t="n">
-        <v>25009</v>
+        <v>22558</v>
       </c>
       <c r="C66" t="n">
-        <v>15.77</v>
+        <v>20.82</v>
       </c>
       <c r="D66" t="n">
-        <v>28531</v>
+        <v>22931</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>98.31</v>
+        <v>25.78</v>
       </c>
       <c r="B67" t="n">
-        <v>44234</v>
+        <v>23892</v>
       </c>
       <c r="C67" t="n">
-        <v>100.46</v>
+        <v>25.56</v>
       </c>
       <c r="D67" t="n">
-        <v>27656</v>
+        <v>20708</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>108.74</v>
+        <v>26.24</v>
       </c>
       <c r="B68" t="n">
-        <v>35203</v>
+        <v>23231</v>
       </c>
       <c r="C68" t="n">
-        <v>105.79</v>
+        <v>23.34</v>
       </c>
       <c r="D68" t="n">
-        <v>26004</v>
+        <v>24154</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>105.1</v>
+        <v>27.01</v>
       </c>
       <c r="B69" t="n">
-        <v>43464</v>
+        <v>21189</v>
       </c>
       <c r="C69" t="n">
-        <v>103.86</v>
+        <v>23.38</v>
       </c>
       <c r="D69" t="n">
-        <v>29379</v>
+        <v>26104</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>109.1</v>
+        <v>27.19</v>
       </c>
       <c r="B70" t="n">
-        <v>35359</v>
+        <v>20702</v>
       </c>
       <c r="C70" t="n">
-        <v>108.32</v>
+        <v>36.61</v>
       </c>
       <c r="D70" t="n">
-        <v>25809</v>
+        <v>17611</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>110.01</v>
+        <v>27.43</v>
       </c>
       <c r="B71" t="n">
-        <v>29948</v>
+        <v>21164</v>
       </c>
       <c r="C71" t="n">
-        <v>108.88</v>
+        <v>29.57</v>
       </c>
       <c r="D71" t="n">
-        <v>15314</v>
+        <v>17938</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>96.7</v>
+        <v>27.58</v>
       </c>
       <c r="B72" t="n">
-        <v>36912</v>
+        <v>22627</v>
       </c>
       <c r="C72" t="n">
-        <v>99.69</v>
+        <v>32.66</v>
       </c>
       <c r="D72" t="n">
-        <v>26996</v>
+        <v>17870</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>108.92</v>
+        <v>27.72</v>
       </c>
       <c r="B73" t="n">
-        <v>34018</v>
+        <v>23929</v>
       </c>
       <c r="C73" t="n">
-        <v>112.68</v>
+        <v>27.88</v>
       </c>
       <c r="D73" t="n">
-        <v>11248</v>
+        <v>11257</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>96.48</v>
+        <v>27.76</v>
       </c>
       <c r="B74" t="n">
-        <v>35854</v>
+        <v>23976</v>
       </c>
       <c r="C74" t="n">
-        <v>97.83</v>
+        <v>20.01</v>
       </c>
       <c r="D74" t="n">
-        <v>21945</v>
+        <v>24222</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>166.79</v>
+        <v>28.67</v>
       </c>
       <c r="B75" t="n">
-        <v>22375</v>
+        <v>21200</v>
       </c>
       <c r="C75" t="n">
-        <v>170.47</v>
+        <v>36.88</v>
       </c>
       <c r="D75" t="n">
-        <v>23622</v>
+        <v>15391</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>45.86</v>
+        <v>28.72</v>
       </c>
       <c r="B76" t="n">
-        <v>23423</v>
+        <v>22112</v>
       </c>
       <c r="C76" t="n">
-        <v>46.93</v>
+        <v>26.5</v>
       </c>
       <c r="D76" t="n">
-        <v>23124</v>
+        <v>15623</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>114.83</v>
+        <v>30.74</v>
       </c>
       <c r="B77" t="n">
-        <v>20160</v>
+        <v>21926</v>
       </c>
       <c r="C77" t="n">
-        <v>113.6</v>
+        <v>41.54</v>
       </c>
       <c r="D77" t="n">
-        <v>16250</v>
+        <v>19107</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>110.81</v>
+        <v>31.17</v>
       </c>
       <c r="B78" t="n">
-        <v>30365</v>
+        <v>20142</v>
       </c>
       <c r="C78" t="n">
-        <v>111.07</v>
+        <v>33.41</v>
       </c>
       <c r="D78" t="n">
-        <v>27844</v>
+        <v>15467</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>108</v>
+        <v>31.37</v>
       </c>
       <c r="B79" t="n">
-        <v>40083</v>
+        <v>20141</v>
       </c>
       <c r="C79" t="n">
-        <v>109.92</v>
+        <v>30.62</v>
       </c>
       <c r="D79" t="n">
-        <v>22453</v>
+        <v>13242</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>178.49</v>
+        <v>31.49</v>
       </c>
       <c r="B80" t="n">
-        <v>25211</v>
+        <v>21274</v>
       </c>
       <c r="C80" t="n">
-        <v>173.29</v>
+        <v>41.91</v>
       </c>
       <c r="D80" t="n">
-        <v>11779</v>
+        <v>25109</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>114.97</v>
+        <v>31.64</v>
       </c>
       <c r="B81" t="n">
-        <v>25323</v>
+        <v>20537</v>
       </c>
       <c r="C81" t="n">
-        <v>117.48</v>
+        <v>35.92</v>
       </c>
       <c r="D81" t="n">
-        <v>24891</v>
+        <v>23183</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>92.47</v>
+        <v>31.96</v>
       </c>
       <c r="B82" t="n">
-        <v>27126</v>
+        <v>20182</v>
       </c>
       <c r="C82" t="n">
-        <v>94.29000000000001</v>
+        <v>21.05</v>
       </c>
       <c r="D82" t="n">
-        <v>17659</v>
+        <v>18361</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>107.54</v>
+        <v>32.57</v>
       </c>
       <c r="B83" t="n">
-        <v>37723</v>
+        <v>22556</v>
       </c>
       <c r="C83" t="n">
-        <v>103.97</v>
+        <v>29.42</v>
       </c>
       <c r="D83" t="n">
-        <v>29322</v>
+        <v>17725</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>106.19</v>
+        <v>33.19</v>
       </c>
       <c r="B84" t="n">
-        <v>42068</v>
+        <v>19853</v>
       </c>
       <c r="C84" t="n">
-        <v>104.79</v>
+        <v>28.47</v>
       </c>
       <c r="D84" t="n">
-        <v>17028</v>
+        <v>19446</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>105.06</v>
+        <v>33.34</v>
       </c>
       <c r="B85" t="n">
-        <v>47985</v>
+        <v>22004</v>
       </c>
       <c r="C85" t="n">
-        <v>103.32</v>
+        <v>32.95</v>
       </c>
       <c r="D85" t="n">
-        <v>12021</v>
+        <v>22071</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>106.11</v>
+        <v>33.37</v>
       </c>
       <c r="B86" t="n">
-        <v>42740</v>
+        <v>23412</v>
       </c>
       <c r="C86" t="n">
-        <v>107.82</v>
+        <v>31.45</v>
       </c>
       <c r="D86" t="n">
-        <v>18959</v>
+        <v>28982</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>176.67</v>
+        <v>33.92</v>
       </c>
       <c r="B87" t="n">
-        <v>22300</v>
+        <v>20402</v>
       </c>
       <c r="C87" t="n">
-        <v>174.17</v>
+        <v>28.28</v>
       </c>
       <c r="D87" t="n">
-        <v>29440</v>
+        <v>11330</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>100.86</v>
+        <v>34.18</v>
       </c>
       <c r="B88" t="n">
-        <v>44676</v>
+        <v>21944</v>
       </c>
       <c r="C88" t="n">
-        <v>101.24</v>
+        <v>36.5</v>
       </c>
       <c r="D88" t="n">
-        <v>29801</v>
+        <v>16853</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>96.84</v>
+        <v>35.05</v>
       </c>
       <c r="B89" t="n">
-        <v>37400</v>
+        <v>17575</v>
       </c>
       <c r="C89" t="n">
-        <v>99.66</v>
+        <v>41.53</v>
       </c>
       <c r="D89" t="n">
-        <v>17757</v>
+        <v>13730</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>98.56999999999999</v>
+        <v>35.08</v>
       </c>
       <c r="B90" t="n">
-        <v>43760</v>
+        <v>23503</v>
       </c>
       <c r="C90" t="n">
-        <v>99.06</v>
+        <v>34.47</v>
       </c>
       <c r="D90" t="n">
-        <v>15811</v>
+        <v>11787</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>93.34999999999999</v>
+        <v>35.29</v>
       </c>
       <c r="B91" t="n">
-        <v>31193</v>
+        <v>20701</v>
       </c>
       <c r="C91" t="n">
-        <v>92.59999999999999</v>
+        <v>39.83</v>
       </c>
       <c r="D91" t="n">
-        <v>19731</v>
+        <v>11509</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>95.75</v>
+        <v>35.6</v>
       </c>
       <c r="B92" t="n">
-        <v>35839</v>
+        <v>21138</v>
       </c>
       <c r="C92" t="n">
-        <v>94.20999999999999</v>
+        <v>34.24</v>
       </c>
       <c r="D92" t="n">
-        <v>19670</v>
+        <v>24670</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>97.04000000000001</v>
+        <v>35.81</v>
       </c>
       <c r="B93" t="n">
-        <v>39272</v>
+        <v>24038</v>
       </c>
       <c r="C93" t="n">
-        <v>96.22</v>
+        <v>29.12</v>
       </c>
       <c r="D93" t="n">
-        <v>28703</v>
+        <v>17356</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>109.22</v>
+        <v>35.86</v>
       </c>
       <c r="B94" t="n">
-        <v>36806</v>
+        <v>20855</v>
       </c>
       <c r="C94" t="n">
-        <v>108.72</v>
+        <v>34.08</v>
       </c>
       <c r="D94" t="n">
-        <v>21809</v>
+        <v>19003</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>90.52</v>
+        <v>36.4</v>
       </c>
       <c r="B95" t="n">
-        <v>21934</v>
+        <v>21155</v>
       </c>
       <c r="C95" t="n">
-        <v>93.5</v>
+        <v>39.62</v>
       </c>
       <c r="D95" t="n">
-        <v>13091</v>
+        <v>22540</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>111.19</v>
+        <v>36.6</v>
       </c>
       <c r="B96" t="n">
-        <v>27303</v>
+        <v>21531</v>
       </c>
       <c r="C96" t="n">
-        <v>111.47</v>
+        <v>34.49</v>
       </c>
       <c r="D96" t="n">
-        <v>12108</v>
+        <v>11507</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>32.48</v>
+        <v>36.84</v>
       </c>
       <c r="B97" t="n">
-        <v>20751</v>
+        <v>22777</v>
       </c>
       <c r="C97" t="n">
-        <v>33.13</v>
+        <v>42.06</v>
       </c>
       <c r="D97" t="n">
-        <v>17812</v>
+        <v>28887</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>92</v>
+        <v>37.07</v>
       </c>
       <c r="B98" t="n">
-        <v>26703</v>
+        <v>22746</v>
       </c>
       <c r="C98" t="n">
-        <v>89.48</v>
+        <v>38.16</v>
       </c>
       <c r="D98" t="n">
-        <v>24717</v>
+        <v>10153</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>114.84</v>
+        <v>37.73</v>
       </c>
       <c r="B99" t="n">
-        <v>24831</v>
+        <v>21917</v>
       </c>
       <c r="C99" t="n">
-        <v>111.4</v>
+        <v>36.77</v>
       </c>
       <c r="D99" t="n">
-        <v>28804</v>
+        <v>21347</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>94.48</v>
+        <v>37.98</v>
       </c>
       <c r="B100" t="n">
-        <v>31641</v>
+        <v>20461</v>
       </c>
       <c r="C100" t="n">
-        <v>93.40000000000001</v>
+        <v>35.75</v>
       </c>
       <c r="D100" t="n">
-        <v>25573</v>
+        <v>15642</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>101.97</v>
+        <v>38.11</v>
       </c>
       <c r="B101" t="n">
-        <v>46715</v>
+        <v>22013</v>
       </c>
       <c r="C101" t="n">
-        <v>101.14</v>
+        <v>35.99</v>
       </c>
       <c r="D101" t="n">
-        <v>14203</v>
+        <v>23690</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>139.82</v>
+        <v>38.23</v>
       </c>
       <c r="B102" t="n">
-        <v>23825</v>
+        <v>20778</v>
       </c>
       <c r="C102" t="n">
-        <v>140.5</v>
+        <v>27.79</v>
       </c>
       <c r="D102" t="n">
-        <v>23307</v>
+        <v>23902</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>109.9</v>
+        <v>38.69</v>
       </c>
       <c r="B103" t="n">
-        <v>32526</v>
+        <v>20140</v>
       </c>
       <c r="C103" t="n">
-        <v>110.45</v>
+        <v>41.36</v>
       </c>
       <c r="D103" t="n">
-        <v>26305</v>
+        <v>25127</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>96.87</v>
+        <v>39.06</v>
       </c>
       <c r="B104" t="n">
-        <v>37662</v>
+        <v>22026</v>
       </c>
       <c r="C104" t="n">
-        <v>100.78</v>
+        <v>32.41</v>
       </c>
       <c r="D104" t="n">
-        <v>12080</v>
+        <v>18516</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>110.13</v>
+        <v>39.32</v>
       </c>
       <c r="B105" t="n">
-        <v>34141</v>
+        <v>23581</v>
       </c>
       <c r="C105" t="n">
-        <v>106.62</v>
+        <v>35.01</v>
       </c>
       <c r="D105" t="n">
-        <v>24251</v>
+        <v>19290</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>112.79</v>
+        <v>39.68</v>
       </c>
       <c r="B106" t="n">
-        <v>26139</v>
+        <v>21804</v>
       </c>
       <c r="C106" t="n">
-        <v>113.24</v>
+        <v>28.83</v>
       </c>
       <c r="D106" t="n">
-        <v>18061</v>
+        <v>28919</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>91.92</v>
+        <v>39.72</v>
       </c>
       <c r="B107" t="n">
-        <v>25005</v>
+        <v>20875</v>
       </c>
       <c r="C107" t="n">
-        <v>92.89</v>
+        <v>32.87</v>
       </c>
       <c r="D107" t="n">
-        <v>27742</v>
+        <v>13353</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>8.449999999999999</v>
+        <v>40.56</v>
       </c>
       <c r="B108" t="n">
-        <v>22838</v>
+        <v>20669</v>
       </c>
       <c r="C108" t="n">
-        <v>8.130000000000001</v>
+        <v>42.3</v>
       </c>
       <c r="D108" t="n">
-        <v>10446</v>
+        <v>15199</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>17.53</v>
+        <v>41.09</v>
       </c>
       <c r="B109" t="n">
-        <v>24395</v>
+        <v>23743</v>
       </c>
       <c r="C109" t="n">
-        <v>17.98</v>
+        <v>46.13</v>
       </c>
       <c r="D109" t="n">
-        <v>10051</v>
+        <v>25465</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>106.58</v>
+        <v>41.22</v>
       </c>
       <c r="B110" t="n">
-        <v>40073</v>
+        <v>23675</v>
       </c>
       <c r="C110" t="n">
-        <v>105.16</v>
+        <v>47.17</v>
       </c>
       <c r="D110" t="n">
-        <v>19047</v>
+        <v>16062</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>90.83</v>
+        <v>42.26</v>
       </c>
       <c r="B111" t="n">
-        <v>26233</v>
+        <v>24117</v>
       </c>
       <c r="C111" t="n">
-        <v>91.66</v>
+        <v>51.25</v>
       </c>
       <c r="D111" t="n">
-        <v>13423</v>
+        <v>25025</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>32.3</v>
+        <v>43.2</v>
       </c>
       <c r="B112" t="n">
-        <v>25083</v>
+        <v>19303</v>
       </c>
       <c r="C112" t="n">
-        <v>32.69</v>
+        <v>35.89</v>
       </c>
       <c r="D112" t="n">
-        <v>26543</v>
+        <v>23700</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>110.68</v>
+        <v>43.58</v>
       </c>
       <c r="B113" t="n">
-        <v>32203</v>
+        <v>20352</v>
       </c>
       <c r="C113" t="n">
-        <v>112.12</v>
+        <v>50.64</v>
       </c>
       <c r="D113" t="n">
-        <v>22288</v>
+        <v>27448</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>104.2</v>
+        <v>44.53</v>
       </c>
       <c r="B114" t="n">
-        <v>47369</v>
+        <v>19654</v>
       </c>
       <c r="C114" t="n">
-        <v>101.2</v>
+        <v>47.42</v>
       </c>
       <c r="D114" t="n">
-        <v>16377</v>
+        <v>17868</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>100.94</v>
+        <v>45.44</v>
       </c>
       <c r="B115" t="n">
-        <v>45394</v>
+        <v>19856</v>
       </c>
       <c r="C115" t="n">
-        <v>101.72</v>
+        <v>54.68</v>
       </c>
       <c r="D115" t="n">
-        <v>21232</v>
+        <v>12528</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>105.88</v>
+        <v>45.86</v>
       </c>
       <c r="B116" t="n">
-        <v>45344</v>
+        <v>22226</v>
       </c>
       <c r="C116" t="n">
-        <v>107.77</v>
+        <v>54.83</v>
       </c>
       <c r="D116" t="n">
-        <v>11944</v>
+        <v>15710</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>111.52</v>
+        <v>45.87</v>
       </c>
       <c r="B117" t="n">
-        <v>29762</v>
+        <v>21189</v>
       </c>
       <c r="C117" t="n">
-        <v>108.46</v>
+        <v>42.53</v>
       </c>
       <c r="D117" t="n">
-        <v>27100</v>
+        <v>28294</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>95.95999999999999</v>
+        <v>46.08</v>
       </c>
       <c r="B118" t="n">
-        <v>36344</v>
+        <v>22187</v>
       </c>
       <c r="C118" t="n">
-        <v>92.15000000000001</v>
+        <v>48.04</v>
       </c>
       <c r="D118" t="n">
-        <v>10952</v>
+        <v>24522</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>17.98</v>
+        <v>46.21</v>
       </c>
       <c r="B119" t="n">
-        <v>24208</v>
+        <v>20265</v>
       </c>
       <c r="C119" t="n">
-        <v>17.43</v>
+        <v>54.19</v>
       </c>
       <c r="D119" t="n">
-        <v>17402</v>
+        <v>13458</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>46.22</v>
+        <v>46.52</v>
       </c>
       <c r="B120" t="n">
-        <v>23271</v>
+        <v>23191</v>
       </c>
       <c r="C120" t="n">
-        <v>45.24</v>
+        <v>32</v>
       </c>
       <c r="D120" t="n">
-        <v>11876</v>
+        <v>13700</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>104.15</v>
+        <v>46.55</v>
       </c>
       <c r="B121" t="n">
-        <v>48473</v>
+        <v>19186</v>
       </c>
       <c r="C121" t="n">
-        <v>108.71</v>
+        <v>33.57</v>
       </c>
       <c r="D121" t="n">
-        <v>27084</v>
+        <v>12169</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>100.81</v>
+        <v>47.22</v>
       </c>
       <c r="B122" t="n">
-        <v>47088</v>
+        <v>22305</v>
       </c>
       <c r="C122" t="n">
-        <v>99.04000000000001</v>
+        <v>52.78</v>
       </c>
       <c r="D122" t="n">
-        <v>26946</v>
+        <v>29696</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>45.13</v>
+        <v>47.29</v>
       </c>
       <c r="B123" t="n">
-        <v>23905</v>
+        <v>21353</v>
       </c>
       <c r="C123" t="n">
-        <v>47.19</v>
+        <v>35.94</v>
       </c>
       <c r="D123" t="n">
-        <v>18362</v>
+        <v>24944</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>101.82</v>
+        <v>47.51</v>
       </c>
       <c r="B124" t="n">
-        <v>47546</v>
+        <v>21715</v>
       </c>
       <c r="C124" t="n">
-        <v>98.52</v>
+        <v>38.75</v>
       </c>
       <c r="D124" t="n">
-        <v>28894</v>
+        <v>28908</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>97.94</v>
+        <v>47.59</v>
       </c>
       <c r="B125" t="n">
-        <v>42987</v>
+        <v>20830</v>
       </c>
       <c r="C125" t="n">
-        <v>101.77</v>
+        <v>42.79</v>
       </c>
       <c r="D125" t="n">
-        <v>21646</v>
+        <v>23368</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>114.54</v>
+        <v>47.72</v>
       </c>
       <c r="B126" t="n">
-        <v>23650</v>
+        <v>22736</v>
       </c>
       <c r="C126" t="n">
-        <v>115.5</v>
+        <v>45.56</v>
       </c>
       <c r="D126" t="n">
-        <v>14842</v>
+        <v>22869</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>98.03</v>
+        <v>48.49</v>
       </c>
       <c r="B127" t="n">
-        <v>41960</v>
+        <v>22233</v>
       </c>
       <c r="C127" t="n">
-        <v>100.31</v>
+        <v>54.97</v>
       </c>
       <c r="D127" t="n">
-        <v>13144</v>
+        <v>13470</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>113.12</v>
+        <v>49.04</v>
       </c>
       <c r="B128" t="n">
-        <v>24587</v>
+        <v>21107</v>
       </c>
       <c r="C128" t="n">
-        <v>107.74</v>
+        <v>57.56</v>
       </c>
       <c r="D128" t="n">
-        <v>25271</v>
+        <v>11453</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>92.72</v>
+        <v>49.27</v>
       </c>
       <c r="B129" t="n">
-        <v>29230</v>
+        <v>19956</v>
       </c>
       <c r="C129" t="n">
-        <v>89.45999999999999</v>
+        <v>50.3</v>
       </c>
       <c r="D129" t="n">
-        <v>29735</v>
+        <v>16567</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>94.63</v>
+        <v>49.78</v>
       </c>
       <c r="B130" t="n">
-        <v>30076</v>
+        <v>22497</v>
       </c>
       <c r="C130" t="n">
-        <v>94.38</v>
+        <v>44.03</v>
       </c>
       <c r="D130" t="n">
-        <v>14367</v>
+        <v>23374</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>110.08</v>
+        <v>49.99</v>
       </c>
       <c r="B131" t="n">
-        <v>33231</v>
+        <v>22886</v>
       </c>
       <c r="C131" t="n">
-        <v>109.1</v>
+        <v>55.55</v>
       </c>
       <c r="D131" t="n">
-        <v>28765</v>
+        <v>28206</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>97.34999999999999</v>
+        <v>50.38</v>
       </c>
       <c r="B132" t="n">
-        <v>41251</v>
+        <v>20622</v>
       </c>
       <c r="C132" t="n">
-        <v>94.64</v>
+        <v>55.61</v>
       </c>
       <c r="D132" t="n">
-        <v>20524</v>
+        <v>23638</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>94.8</v>
+        <v>50.4</v>
       </c>
       <c r="B133" t="n">
-        <v>33328</v>
+        <v>21315</v>
       </c>
       <c r="C133" t="n">
-        <v>97.41</v>
+        <v>52.09</v>
       </c>
       <c r="D133" t="n">
-        <v>23082</v>
+        <v>25310</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>110.85</v>
+        <v>50.77</v>
       </c>
       <c r="B134" t="n">
-        <v>30551</v>
+        <v>21401</v>
       </c>
       <c r="C134" t="n">
-        <v>110.24</v>
+        <v>56.42</v>
       </c>
       <c r="D134" t="n">
-        <v>22258</v>
+        <v>10629</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>105.14</v>
+        <v>50.96</v>
       </c>
       <c r="B135" t="n">
-        <v>46626</v>
+        <v>21217</v>
       </c>
       <c r="C135" t="n">
-        <v>108.3</v>
+        <v>49.96</v>
       </c>
       <c r="D135" t="n">
-        <v>18506</v>
+        <v>23833</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>90.78</v>
+        <v>51.07</v>
       </c>
       <c r="B136" t="n">
-        <v>24855</v>
+        <v>20438</v>
       </c>
       <c r="C136" t="n">
-        <v>93.51000000000001</v>
+        <v>64.88</v>
       </c>
       <c r="D136" t="n">
-        <v>27823</v>
+        <v>14058</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>94.31</v>
+        <v>51.22</v>
       </c>
       <c r="B137" t="n">
-        <v>30651</v>
+        <v>20620</v>
       </c>
       <c r="C137" t="n">
-        <v>93.86</v>
+        <v>52.7</v>
       </c>
       <c r="D137" t="n">
-        <v>29308</v>
+        <v>13979</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>97.08</v>
+        <v>51.38</v>
       </c>
       <c r="B138" t="n">
-        <v>39895</v>
+        <v>22231</v>
       </c>
       <c r="C138" t="n">
-        <v>93.93000000000001</v>
+        <v>39.22</v>
       </c>
       <c r="D138" t="n">
-        <v>14808</v>
+        <v>23474</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>157.78</v>
+        <v>51.82</v>
       </c>
       <c r="B139" t="n">
-        <v>22619</v>
+        <v>21817</v>
       </c>
       <c r="C139" t="n">
-        <v>161.65</v>
+        <v>48.9</v>
       </c>
       <c r="D139" t="n">
-        <v>14135</v>
+        <v>14962</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>95.26000000000001</v>
+        <v>52.28</v>
       </c>
       <c r="B140" t="n">
-        <v>37113</v>
+        <v>22030</v>
       </c>
       <c r="C140" t="n">
-        <v>99.67</v>
+        <v>48.1</v>
       </c>
       <c r="D140" t="n">
-        <v>21076</v>
+        <v>17691</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>101.75</v>
+        <v>52.75</v>
       </c>
       <c r="B141" t="n">
-        <v>47509</v>
+        <v>22230</v>
       </c>
       <c r="C141" t="n">
-        <v>104.93</v>
+        <v>62.53</v>
       </c>
       <c r="D141" t="n">
-        <v>25399</v>
+        <v>22052</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>114.3</v>
+        <v>53.22</v>
       </c>
       <c r="B142" t="n">
-        <v>24383</v>
+        <v>22444</v>
       </c>
       <c r="C142" t="n">
-        <v>116.68</v>
+        <v>43.76</v>
       </c>
       <c r="D142" t="n">
-        <v>17545</v>
+        <v>16401</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>110.46</v>
+        <v>53.56</v>
       </c>
       <c r="B143" t="n">
-        <v>29974</v>
+        <v>20258</v>
       </c>
       <c r="C143" t="n">
-        <v>108.4</v>
+        <v>34.36</v>
       </c>
       <c r="D143" t="n">
-        <v>29606</v>
+        <v>23772</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>112.77</v>
+        <v>54.15</v>
       </c>
       <c r="B144" t="n">
-        <v>28561</v>
+        <v>21194</v>
       </c>
       <c r="C144" t="n">
-        <v>111.27</v>
+        <v>49.53</v>
       </c>
       <c r="D144" t="n">
-        <v>17333</v>
+        <v>13830</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>105.09</v>
+        <v>54.67</v>
       </c>
       <c r="B145" t="n">
-        <v>44415</v>
+        <v>21402</v>
       </c>
       <c r="C145" t="n">
-        <v>104.73</v>
+        <v>56.12</v>
       </c>
       <c r="D145" t="n">
-        <v>13153</v>
+        <v>18672</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>107.71</v>
+        <v>55.34</v>
       </c>
       <c r="B146" t="n">
-        <v>39858</v>
+        <v>21705</v>
       </c>
       <c r="C146" t="n">
-        <v>104.1</v>
+        <v>52.57</v>
       </c>
       <c r="D146" t="n">
-        <v>16638</v>
+        <v>28353</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>92.40000000000001</v>
+        <v>55.76</v>
       </c>
       <c r="B147" t="n">
-        <v>27407</v>
+        <v>21342</v>
       </c>
       <c r="C147" t="n">
-        <v>92.58</v>
+        <v>53.69</v>
       </c>
       <c r="D147" t="n">
-        <v>20933</v>
+        <v>16709</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>105.91</v>
+        <v>56.02</v>
       </c>
       <c r="B148" t="n">
-        <v>46450</v>
+        <v>20977</v>
       </c>
       <c r="C148" t="n">
-        <v>109.76</v>
+        <v>59.07</v>
       </c>
       <c r="D148" t="n">
-        <v>10298</v>
+        <v>19158</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>135.18</v>
+        <v>56.03</v>
       </c>
       <c r="B149" t="n">
-        <v>24922</v>
+        <v>20157</v>
       </c>
       <c r="C149" t="n">
-        <v>130.66</v>
+        <v>51.59</v>
       </c>
       <c r="D149" t="n">
-        <v>27068</v>
+        <v>15940</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>114.57</v>
+        <v>56.48</v>
       </c>
       <c r="B150" t="n">
-        <v>24095</v>
+        <v>22448</v>
       </c>
       <c r="C150" t="n">
-        <v>115.82</v>
+        <v>64.8</v>
       </c>
       <c r="D150" t="n">
-        <v>26868</v>
+        <v>19892</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>91.72</v>
+        <v>57.23</v>
       </c>
       <c r="B151" t="n">
-        <v>24829</v>
+        <v>21811</v>
       </c>
       <c r="C151" t="n">
-        <v>89.47</v>
+        <v>68.77</v>
       </c>
       <c r="D151" t="n">
-        <v>11653</v>
+        <v>25729</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>113.28</v>
+        <v>57.58</v>
       </c>
       <c r="B152" t="n">
-        <v>26115</v>
+        <v>19329</v>
       </c>
       <c r="C152" t="n">
-        <v>115.69</v>
+        <v>51.63</v>
       </c>
       <c r="D152" t="n">
-        <v>18834</v>
+        <v>11440</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>98.53</v>
+        <v>57.62</v>
       </c>
       <c r="B153" t="n">
-        <v>40547</v>
+        <v>20470</v>
       </c>
       <c r="C153" t="n">
-        <v>96.34999999999999</v>
+        <v>61.29</v>
       </c>
       <c r="D153" t="n">
-        <v>25187</v>
+        <v>23766</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>93.09999999999999</v>
+        <v>57.73</v>
       </c>
       <c r="B154" t="n">
-        <v>27300</v>
+        <v>21598</v>
       </c>
       <c r="C154" t="n">
-        <v>91.29000000000001</v>
+        <v>59.18</v>
       </c>
       <c r="D154" t="n">
-        <v>10704</v>
+        <v>23026</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>105.69</v>
+        <v>57.81</v>
       </c>
       <c r="B155" t="n">
-        <v>44755</v>
+        <v>19540</v>
       </c>
       <c r="C155" t="n">
-        <v>108.73</v>
+        <v>47.01</v>
       </c>
       <c r="D155" t="n">
-        <v>22355</v>
+        <v>20444</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>103.03</v>
+        <v>58.27</v>
       </c>
       <c r="B156" t="n">
-        <v>49854</v>
+        <v>18561</v>
       </c>
       <c r="C156" t="n">
-        <v>106.94</v>
+        <v>51.52</v>
       </c>
       <c r="D156" t="n">
-        <v>13388</v>
+        <v>12129</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>110.14</v>
+        <v>58.35</v>
       </c>
       <c r="B157" t="n">
-        <v>33152</v>
+        <v>21845</v>
       </c>
       <c r="C157" t="n">
-        <v>107.93</v>
+        <v>56.1</v>
       </c>
       <c r="D157" t="n">
-        <v>27985</v>
+        <v>28012</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>95.95</v>
+        <v>58.82</v>
       </c>
       <c r="B158" t="n">
-        <v>34324</v>
+        <v>17476</v>
       </c>
       <c r="C158" t="n">
-        <v>98.38</v>
+        <v>66.39</v>
       </c>
       <c r="D158" t="n">
-        <v>19078</v>
+        <v>29855</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>106.3</v>
+        <v>59.48</v>
       </c>
       <c r="B159" t="n">
-        <v>43156</v>
+        <v>21146</v>
       </c>
       <c r="C159" t="n">
-        <v>106.04</v>
+        <v>78.5</v>
       </c>
       <c r="D159" t="n">
-        <v>26240</v>
+        <v>28122</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>90.45</v>
+        <v>59.67</v>
       </c>
       <c r="B160" t="n">
-        <v>25811</v>
+        <v>21682</v>
       </c>
       <c r="C160" t="n">
-        <v>94.14</v>
+        <v>67.14</v>
       </c>
       <c r="D160" t="n">
-        <v>17200</v>
+        <v>20002</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>111.42</v>
+        <v>59.82</v>
       </c>
       <c r="B161" t="n">
-        <v>29518</v>
+        <v>21569</v>
       </c>
       <c r="C161" t="n">
-        <v>110.54</v>
+        <v>50.67</v>
       </c>
       <c r="D161" t="n">
-        <v>19009</v>
+        <v>19737</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>92.5</v>
+        <v>59.84</v>
       </c>
       <c r="B162" t="n">
-        <v>27369</v>
+        <v>20554</v>
       </c>
       <c r="C162" t="n">
-        <v>90.88</v>
+        <v>59.96</v>
       </c>
       <c r="D162" t="n">
-        <v>14558</v>
+        <v>16330</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>90.81999999999999</v>
+        <v>60.3</v>
       </c>
       <c r="B163" t="n">
-        <v>27200</v>
+        <v>19417</v>
       </c>
       <c r="C163" t="n">
-        <v>93.09</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="D163" t="n">
-        <v>20768</v>
+        <v>18598</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>110.53</v>
+        <v>61.14</v>
       </c>
       <c r="B164" t="n">
-        <v>30031</v>
+        <v>19303</v>
       </c>
       <c r="C164" t="n">
-        <v>110.57</v>
+        <v>60.9</v>
       </c>
       <c r="D164" t="n">
-        <v>13654</v>
+        <v>12626</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>91.83</v>
+        <v>61.33</v>
       </c>
       <c r="B165" t="n">
-        <v>26881</v>
+        <v>20893</v>
       </c>
       <c r="C165" t="n">
-        <v>92.06</v>
+        <v>55.14</v>
       </c>
       <c r="D165" t="n">
-        <v>15785</v>
+        <v>27367</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>113.35</v>
+        <v>61.52</v>
       </c>
       <c r="B166" t="n">
-        <v>26294</v>
+        <v>20195</v>
       </c>
       <c r="C166" t="n">
-        <v>108.89</v>
+        <v>68.22</v>
       </c>
       <c r="D166" t="n">
-        <v>27297</v>
+        <v>25661</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>113.13</v>
+        <v>62.31</v>
       </c>
       <c r="B167" t="n">
-        <v>25185</v>
+        <v>21184</v>
       </c>
       <c r="C167" t="n">
-        <v>116.3</v>
+        <v>53.01</v>
       </c>
       <c r="D167" t="n">
-        <v>14056</v>
+        <v>24202</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>107.34</v>
+        <v>62.59</v>
       </c>
       <c r="B168" t="n">
-        <v>39815</v>
+        <v>20281</v>
       </c>
       <c r="C168" t="n">
-        <v>110.56</v>
+        <v>55.97</v>
       </c>
       <c r="D168" t="n">
-        <v>15576</v>
+        <v>29855</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>114.5</v>
+        <v>63</v>
       </c>
       <c r="B169" t="n">
-        <v>23633</v>
+        <v>20664</v>
       </c>
       <c r="C169" t="n">
-        <v>120.22</v>
+        <v>57.25</v>
       </c>
       <c r="D169" t="n">
-        <v>12067</v>
+        <v>24438</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>92.72</v>
+        <v>63.25</v>
       </c>
       <c r="B170" t="n">
-        <v>25760</v>
+        <v>18799</v>
       </c>
       <c r="C170" t="n">
-        <v>94.95</v>
+        <v>69.8</v>
       </c>
       <c r="D170" t="n">
-        <v>11963</v>
+        <v>14373</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>94.84</v>
+        <v>63.8</v>
       </c>
       <c r="B171" t="n">
-        <v>31682</v>
+        <v>21476</v>
       </c>
       <c r="C171" t="n">
-        <v>92.45999999999999</v>
+        <v>73.09</v>
       </c>
       <c r="D171" t="n">
-        <v>10743</v>
+        <v>28222</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>173.58</v>
+        <v>63.82</v>
       </c>
       <c r="B172" t="n">
-        <v>22518</v>
+        <v>20513</v>
       </c>
       <c r="C172" t="n">
-        <v>172.53</v>
+        <v>52.25</v>
       </c>
       <c r="D172" t="n">
-        <v>11615</v>
+        <v>10349</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>93.62</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="B173" t="n">
-        <v>28894</v>
+        <v>20902</v>
       </c>
       <c r="C173" t="n">
-        <v>95.23999999999999</v>
+        <v>68.69</v>
       </c>
       <c r="D173" t="n">
-        <v>17489</v>
+        <v>28044</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>90.48999999999999</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="B174" t="n">
-        <v>23499</v>
+        <v>20848</v>
       </c>
       <c r="C174" t="n">
-        <v>93.98</v>
+        <v>52.88</v>
       </c>
       <c r="D174" t="n">
-        <v>10937</v>
+        <v>10508</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>102.93</v>
+        <v>65.64</v>
       </c>
       <c r="B175" t="n">
-        <v>45452</v>
+        <v>20626</v>
       </c>
       <c r="C175" t="n">
-        <v>101.08</v>
+        <v>74.44</v>
       </c>
       <c r="D175" t="n">
-        <v>25684</v>
+        <v>25415</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>95.12</v>
+        <v>66.87</v>
       </c>
       <c r="B176" t="n">
-        <v>36013</v>
+        <v>19837</v>
       </c>
       <c r="C176" t="n">
-        <v>97.83</v>
+        <v>69.25</v>
       </c>
       <c r="D176" t="n">
-        <v>12099</v>
+        <v>20583</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>103.87</v>
+        <v>67.03</v>
       </c>
       <c r="B177" t="n">
-        <v>48658</v>
+        <v>20672</v>
       </c>
       <c r="C177" t="n">
-        <v>100.48</v>
+        <v>76.42</v>
       </c>
       <c r="D177" t="n">
-        <v>29945</v>
+        <v>15043</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>109.01</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="B178" t="n">
-        <v>35499</v>
+        <v>20390</v>
       </c>
       <c r="C178" t="n">
-        <v>112.42</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D178" t="n">
-        <v>12294</v>
+        <v>23693</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>164.22</v>
+        <v>67.38</v>
       </c>
       <c r="B179" t="n">
-        <v>21370</v>
+        <v>21761</v>
       </c>
       <c r="C179" t="n">
-        <v>166.87</v>
+        <v>77.12</v>
       </c>
       <c r="D179" t="n">
-        <v>27186</v>
+        <v>28717</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>97.48</v>
+        <v>67.7</v>
       </c>
       <c r="B180" t="n">
-        <v>39309</v>
+        <v>19337</v>
       </c>
       <c r="C180" t="n">
-        <v>99.40000000000001</v>
+        <v>56.66</v>
       </c>
       <c r="D180" t="n">
-        <v>17134</v>
+        <v>16210</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>90.14</v>
+        <v>68.61</v>
       </c>
       <c r="B181" t="n">
-        <v>24023</v>
+        <v>19942</v>
       </c>
       <c r="C181" t="n">
-        <v>88.77</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="D181" t="n">
-        <v>21571</v>
+        <v>16069</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121.63</v>
+        <v>69.19</v>
       </c>
       <c r="B182" t="n">
-        <v>24290</v>
+        <v>20631</v>
       </c>
       <c r="C182" t="n">
-        <v>119.21</v>
+        <v>53.66</v>
       </c>
       <c r="D182" t="n">
-        <v>20456</v>
+        <v>13129</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>105.7</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="B183" t="n">
-        <v>44778</v>
+        <v>22588</v>
       </c>
       <c r="C183" t="n">
-        <v>105.98</v>
+        <v>72.23</v>
       </c>
       <c r="D183" t="n">
-        <v>10682</v>
+        <v>22703</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>94.86</v>
+        <v>69.75</v>
       </c>
       <c r="B184" t="n">
-        <v>33077</v>
+        <v>21116</v>
       </c>
       <c r="C184" t="n">
-        <v>97.89</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="D184" t="n">
-        <v>18367</v>
+        <v>25353</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>111.59</v>
+        <v>70.27</v>
       </c>
       <c r="B185" t="n">
-        <v>28676</v>
+        <v>19921</v>
       </c>
       <c r="C185" t="n">
-        <v>108.4</v>
+        <v>72.36</v>
       </c>
       <c r="D185" t="n">
-        <v>12949</v>
+        <v>11621</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>105.75</v>
+        <v>70.34</v>
       </c>
       <c r="B186" t="n">
-        <v>43894</v>
+        <v>20161</v>
       </c>
       <c r="C186" t="n">
-        <v>109.55</v>
+        <v>73.97</v>
       </c>
       <c r="D186" t="n">
-        <v>25761</v>
+        <v>13720</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>106.77</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="B187" t="n">
-        <v>42644</v>
+        <v>21910</v>
       </c>
       <c r="C187" t="n">
-        <v>109.09</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="D187" t="n">
-        <v>25650</v>
+        <v>10927</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>108.46</v>
+        <v>70.8</v>
       </c>
       <c r="B188" t="n">
-        <v>36039</v>
+        <v>19628</v>
       </c>
       <c r="C188" t="n">
-        <v>108.41</v>
+        <v>83.94</v>
       </c>
       <c r="D188" t="n">
-        <v>14064</v>
+        <v>24640</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>92.19</v>
+        <v>70.81</v>
       </c>
       <c r="B189" t="n">
-        <v>26135</v>
+        <v>20490</v>
       </c>
       <c r="C189" t="n">
-        <v>92.41</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="D189" t="n">
-        <v>18217</v>
+        <v>11750</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>111.26</v>
+        <v>70.92</v>
       </c>
       <c r="B190" t="n">
-        <v>27942</v>
+        <v>21371</v>
       </c>
       <c r="C190" t="n">
-        <v>108.48</v>
+        <v>67.25</v>
       </c>
       <c r="D190" t="n">
-        <v>10212</v>
+        <v>13239</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>104.35</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="B191" t="n">
-        <v>45796</v>
+        <v>18863</v>
       </c>
       <c r="C191" t="n">
-        <v>107.43</v>
+        <v>64.58</v>
       </c>
       <c r="D191" t="n">
-        <v>24011</v>
+        <v>28494</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>102.9</v>
+        <v>72.08</v>
       </c>
       <c r="B192" t="n">
-        <v>45722</v>
+        <v>20896</v>
       </c>
       <c r="C192" t="n">
-        <v>106.78</v>
+        <v>59.57</v>
       </c>
       <c r="D192" t="n">
-        <v>22120</v>
+        <v>18086</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>99.2</v>
+        <v>72.48</v>
       </c>
       <c r="B193" t="n">
-        <v>43119</v>
+        <v>19399</v>
       </c>
       <c r="C193" t="n">
-        <v>100.77</v>
+        <v>71.8</v>
       </c>
       <c r="D193" t="n">
-        <v>15543</v>
+        <v>26986</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>102.45</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="B194" t="n">
-        <v>47504</v>
+        <v>21639</v>
       </c>
       <c r="C194" t="n">
-        <v>101.76</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="D194" t="n">
-        <v>22435</v>
+        <v>16222</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>93.77</v>
+        <v>72.84</v>
       </c>
       <c r="B195" t="n">
-        <v>30849</v>
+        <v>19595</v>
       </c>
       <c r="C195" t="n">
-        <v>92.47</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="D195" t="n">
-        <v>27888</v>
+        <v>29174</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>110.92</v>
+        <v>73.39</v>
       </c>
       <c r="B196" t="n">
-        <v>32601</v>
+        <v>20956</v>
       </c>
       <c r="C196" t="n">
-        <v>111.34</v>
+        <v>61.92</v>
       </c>
       <c r="D196" t="n">
-        <v>27228</v>
+        <v>21903</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>93.45</v>
+        <v>74.39</v>
       </c>
       <c r="B197" t="n">
-        <v>28460</v>
+        <v>20974</v>
       </c>
       <c r="C197" t="n">
-        <v>95.23999999999999</v>
+        <v>70.72</v>
       </c>
       <c r="D197" t="n">
-        <v>29728</v>
+        <v>12232</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>105.9</v>
+        <v>74.66</v>
       </c>
       <c r="B198" t="n">
-        <v>42587</v>
+        <v>20359</v>
       </c>
       <c r="C198" t="n">
-        <v>110.43</v>
+        <v>82.34</v>
       </c>
       <c r="D198" t="n">
-        <v>28779</v>
+        <v>23010</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>102.68</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="B199" t="n">
-        <v>44619</v>
+        <v>20188</v>
       </c>
       <c r="C199" t="n">
-        <v>101.2</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="D199" t="n">
-        <v>17749</v>
+        <v>11402</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>97.34999999999999</v>
+        <v>75.64</v>
       </c>
       <c r="B200" t="n">
-        <v>37648</v>
+        <v>20000</v>
       </c>
       <c r="C200" t="n">
-        <v>95.40000000000001</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="D200" t="n">
-        <v>14501</v>
+        <v>20313</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>99.58</v>
+        <v>75.8</v>
       </c>
       <c r="B201" t="n">
-        <v>46181</v>
+        <v>21002</v>
       </c>
       <c r="C201" t="n">
-        <v>98.20999999999999</v>
+        <v>79.63</v>
       </c>
       <c r="D201" t="n">
-        <v>10912</v>
+        <v>20825</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>114.93</v>
+        <v>76.72</v>
       </c>
       <c r="B202" t="n">
-        <v>23303</v>
+        <v>20967</v>
       </c>
       <c r="C202" t="n">
-        <v>111.19</v>
+        <v>57.26</v>
       </c>
       <c r="D202" t="n">
-        <v>20690</v>
+        <v>19111</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>98.73</v>
+        <v>76.89</v>
       </c>
       <c r="B203" t="n">
-        <v>43358</v>
+        <v>20968</v>
       </c>
       <c r="C203" t="n">
-        <v>98.18000000000001</v>
+        <v>74.72</v>
       </c>
       <c r="D203" t="n">
-        <v>29121</v>
+        <v>27878</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>97.75</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="B204" t="n">
-        <v>42935</v>
+        <v>19929</v>
       </c>
       <c r="C204" t="n">
-        <v>95.34999999999999</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="D204" t="n">
-        <v>25409</v>
+        <v>10219</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>105.33</v>
+        <v>77.48</v>
       </c>
       <c r="B205" t="n">
-        <v>44859</v>
+        <v>19896</v>
       </c>
       <c r="C205" t="n">
-        <v>105.91</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D205" t="n">
-        <v>18152</v>
+        <v>23347</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>91.08</v>
+        <v>78.22</v>
       </c>
       <c r="B206" t="n">
-        <v>27137</v>
+        <v>18977</v>
       </c>
       <c r="C206" t="n">
-        <v>88.25</v>
+        <v>64.62</v>
       </c>
       <c r="D206" t="n">
-        <v>26218</v>
+        <v>21612</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>95.51000000000001</v>
+        <v>78.28</v>
       </c>
       <c r="B207" t="n">
-        <v>35930</v>
+        <v>19946</v>
       </c>
       <c r="C207" t="n">
-        <v>94.47</v>
+        <v>75.3</v>
       </c>
       <c r="D207" t="n">
-        <v>28920</v>
+        <v>16091</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>113.87</v>
+        <v>78.31</v>
       </c>
       <c r="B208" t="n">
-        <v>24844</v>
+        <v>20660</v>
       </c>
       <c r="C208" t="n">
-        <v>114.7</v>
+        <v>84.38</v>
       </c>
       <c r="D208" t="n">
-        <v>15546</v>
+        <v>17492</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>102.74</v>
+        <v>78.34</v>
       </c>
       <c r="B209" t="n">
-        <v>45541</v>
+        <v>20465</v>
       </c>
       <c r="C209" t="n">
-        <v>105.44</v>
+        <v>80.27</v>
       </c>
       <c r="D209" t="n">
-        <v>19395</v>
+        <v>25509</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>96.11</v>
+        <v>78.83</v>
       </c>
       <c r="B210" t="n">
-        <v>36649</v>
+        <v>20871</v>
       </c>
       <c r="C210" t="n">
-        <v>97.34999999999999</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="D210" t="n">
-        <v>29713</v>
+        <v>13586</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>97.3</v>
+        <v>79.2</v>
       </c>
       <c r="B211" t="n">
-        <v>40638</v>
+        <v>19179</v>
       </c>
       <c r="C211" t="n">
-        <v>101.1</v>
+        <v>78.97</v>
       </c>
       <c r="D211" t="n">
-        <v>12155</v>
+        <v>11269</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>22.69</v>
+        <v>79.69</v>
       </c>
       <c r="B212" t="n">
-        <v>23820</v>
+        <v>20651</v>
       </c>
       <c r="C212" t="n">
-        <v>23.64</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="D212" t="n">
-        <v>22149</v>
+        <v>23646</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>105.57</v>
+        <v>80.39</v>
       </c>
       <c r="B213" t="n">
-        <v>46359</v>
+        <v>19767</v>
       </c>
       <c r="C213" t="n">
-        <v>108.28</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D213" t="n">
-        <v>19703</v>
+        <v>14370</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>111.4</v>
+        <v>80.44</v>
       </c>
       <c r="B214" t="n">
-        <v>28562</v>
+        <v>21059</v>
       </c>
       <c r="C214" t="n">
-        <v>114.39</v>
+        <v>91.25</v>
       </c>
       <c r="D214" t="n">
-        <v>12225</v>
+        <v>24581</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>111.19</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="B215" t="n">
-        <v>27516</v>
+        <v>20765</v>
       </c>
       <c r="C215" t="n">
-        <v>108.33</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="D215" t="n">
-        <v>20484</v>
+        <v>21969</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>112.68</v>
+        <v>80.89</v>
       </c>
       <c r="B216" t="n">
-        <v>24590</v>
+        <v>20023</v>
       </c>
       <c r="C216" t="n">
-        <v>108.3</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="D216" t="n">
-        <v>25913</v>
+        <v>10293</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>97.84</v>
+        <v>82.06</v>
       </c>
       <c r="B217" t="n">
-        <v>40569</v>
+        <v>21116</v>
       </c>
       <c r="C217" t="n">
-        <v>97.68000000000001</v>
+        <v>68.56</v>
       </c>
       <c r="D217" t="n">
-        <v>21868</v>
+        <v>14328</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>26.37</v>
+        <v>82.23</v>
       </c>
       <c r="B218" t="n">
-        <v>25783</v>
+        <v>20528</v>
       </c>
       <c r="C218" t="n">
-        <v>26.68</v>
+        <v>77.2</v>
       </c>
       <c r="D218" t="n">
-        <v>22719</v>
+        <v>17281</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>113.96</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="B219" t="n">
-        <v>23046</v>
+        <v>20378</v>
       </c>
       <c r="C219" t="n">
-        <v>111.23</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="D219" t="n">
-        <v>24318</v>
+        <v>24529</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>109.99</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="B220" t="n">
-        <v>31631</v>
+        <v>20503</v>
       </c>
       <c r="C220" t="n">
-        <v>111.76</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="D220" t="n">
-        <v>16747</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>111.03</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="B221" t="n">
-        <v>28568</v>
+        <v>19259</v>
       </c>
       <c r="C221" t="n">
-        <v>107.44</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="D221" t="n">
-        <v>12218</v>
+        <v>20497</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>171.61</v>
+        <v>82.94</v>
       </c>
       <c r="B222" t="n">
-        <v>25529</v>
+        <v>20813</v>
       </c>
       <c r="C222" t="n">
-        <v>166</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="D222" t="n">
-        <v>18374</v>
+        <v>19888</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>5.04</v>
+        <v>83.67</v>
       </c>
       <c r="B223" t="n">
-        <v>23491</v>
+        <v>19951</v>
       </c>
       <c r="C223" t="n">
-        <v>4.7</v>
+        <v>64.47</v>
       </c>
       <c r="D223" t="n">
-        <v>27538</v>
+        <v>23927</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>106.67</v>
+        <v>83.69</v>
       </c>
       <c r="B224" t="n">
-        <v>43106</v>
+        <v>20103</v>
       </c>
       <c r="C224" t="n">
-        <v>102.23</v>
+        <v>91.69</v>
       </c>
       <c r="D224" t="n">
-        <v>29316</v>
+        <v>29877</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>102.6</v>
+        <v>83.75</v>
       </c>
       <c r="B225" t="n">
-        <v>47740</v>
+        <v>20510</v>
       </c>
       <c r="C225" t="n">
-        <v>104.53</v>
+        <v>89.37</v>
       </c>
       <c r="D225" t="n">
-        <v>18786</v>
+        <v>11054</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>114.95</v>
+        <v>83.81</v>
       </c>
       <c r="B226" t="n">
-        <v>22634</v>
+        <v>20592</v>
       </c>
       <c r="C226" t="n">
-        <v>118.21</v>
+        <v>66.48</v>
       </c>
       <c r="D226" t="n">
-        <v>18973</v>
+        <v>18260</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>110.61</v>
+        <v>84.05</v>
       </c>
       <c r="B227" t="n">
-        <v>29864</v>
+        <v>20097</v>
       </c>
       <c r="C227" t="n">
-        <v>112.18</v>
+        <v>98.62</v>
       </c>
       <c r="D227" t="n">
-        <v>20972</v>
+        <v>16117</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>177.2</v>
+        <v>84.58</v>
       </c>
       <c r="B228" t="n">
-        <v>22001</v>
+        <v>19949</v>
       </c>
       <c r="C228" t="n">
-        <v>180</v>
+        <v>95.63</v>
       </c>
       <c r="D228" t="n">
-        <v>17197</v>
+        <v>11475</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>5.61</v>
+        <v>84.64</v>
       </c>
       <c r="B229" t="n">
-        <v>25132</v>
+        <v>20331</v>
       </c>
       <c r="C229" t="n">
-        <v>5.54</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="D229" t="n">
-        <v>14113</v>
+        <v>16138</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>108.73</v>
+        <v>84.69</v>
       </c>
       <c r="B230" t="n">
-        <v>36233</v>
+        <v>20502</v>
       </c>
       <c r="C230" t="n">
-        <v>113.67</v>
+        <v>89.5</v>
       </c>
       <c r="D230" t="n">
-        <v>24310</v>
+        <v>20682</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>92.53</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="B231" t="n">
-        <v>27081</v>
+        <v>19956</v>
       </c>
       <c r="C231" t="n">
-        <v>91.7</v>
+        <v>67.97</v>
       </c>
       <c r="D231" t="n">
-        <v>24381</v>
+        <v>13589</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>95.13</v>
+        <v>85.41</v>
       </c>
       <c r="B232" t="n">
-        <v>33696</v>
+        <v>19482</v>
       </c>
       <c r="C232" t="n">
-        <v>96.93000000000001</v>
+        <v>92.72</v>
       </c>
       <c r="D232" t="n">
-        <v>16704</v>
+        <v>26343</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>147.89</v>
+        <v>85.45</v>
       </c>
       <c r="B233" t="n">
-        <v>20770</v>
+        <v>20065</v>
       </c>
       <c r="C233" t="n">
-        <v>149.47</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="D233" t="n">
-        <v>23014</v>
+        <v>10447</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>105.01</v>
+        <v>86.33</v>
       </c>
       <c r="B234" t="n">
-        <v>45119</v>
+        <v>20315</v>
       </c>
       <c r="C234" t="n">
-        <v>105.55</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="D234" t="n">
-        <v>18193</v>
+        <v>18196</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>109.49</v>
+        <v>87.03</v>
       </c>
       <c r="B235" t="n">
-        <v>33257</v>
+        <v>20809</v>
       </c>
       <c r="C235" t="n">
-        <v>111.69</v>
+        <v>100.68</v>
       </c>
       <c r="D235" t="n">
-        <v>25297</v>
+        <v>11244</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>92.91</v>
+        <v>87.66</v>
       </c>
       <c r="B236" t="n">
-        <v>28200</v>
+        <v>20116</v>
       </c>
       <c r="C236" t="n">
-        <v>94.17</v>
+        <v>101.28</v>
       </c>
       <c r="D236" t="n">
-        <v>25193</v>
+        <v>14603</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>111.48</v>
+        <v>88.41</v>
       </c>
       <c r="B237" t="n">
-        <v>28264</v>
+        <v>20388</v>
       </c>
       <c r="C237" t="n">
-        <v>112</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="D237" t="n">
-        <v>14293</v>
+        <v>12633</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>103.91</v>
+        <v>88.7</v>
       </c>
       <c r="B238" t="n">
-        <v>45212</v>
+        <v>20910</v>
       </c>
       <c r="C238" t="n">
-        <v>103.63</v>
+        <v>93.83</v>
       </c>
       <c r="D238" t="n">
-        <v>21429</v>
+        <v>28324</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>86.31</v>
+        <v>88.7</v>
       </c>
       <c r="B239" t="n">
-        <v>23027</v>
+        <v>20806</v>
       </c>
       <c r="C239" t="n">
-        <v>86.98999999999999</v>
+        <v>90.12</v>
       </c>
       <c r="D239" t="n">
-        <v>26932</v>
+        <v>19934</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>106.96</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="B240" t="n">
-        <v>41586</v>
+        <v>21457</v>
       </c>
       <c r="C240" t="n">
-        <v>106.32</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="D240" t="n">
-        <v>20550</v>
+        <v>10244</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>113.33</v>
+        <v>89.66</v>
       </c>
       <c r="B241" t="n">
-        <v>25263</v>
+        <v>21576</v>
       </c>
       <c r="C241" t="n">
-        <v>111.07</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="D241" t="n">
-        <v>15994</v>
+        <v>23252</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>24.93</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="B242" t="n">
-        <v>22162</v>
+        <v>20733</v>
       </c>
       <c r="C242" t="n">
-        <v>25.22</v>
+        <v>102.64</v>
       </c>
       <c r="D242" t="n">
-        <v>19554</v>
+        <v>26383</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>103.15</v>
+        <v>90.27</v>
       </c>
       <c r="B243" t="n">
-        <v>45147</v>
+        <v>21081</v>
       </c>
       <c r="C243" t="n">
-        <v>104.37</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D243" t="n">
-        <v>19942</v>
+        <v>20183</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>91.42</v>
+        <v>90.61</v>
       </c>
       <c r="B244" t="n">
-        <v>25276</v>
+        <v>20603</v>
       </c>
       <c r="C244" t="n">
-        <v>91.89</v>
+        <v>82.41</v>
       </c>
       <c r="D244" t="n">
-        <v>28937</v>
+        <v>26003</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>108.72</v>
+        <v>90.62</v>
       </c>
       <c r="B245" t="n">
-        <v>36245</v>
+        <v>21452</v>
       </c>
       <c r="C245" t="n">
-        <v>106.93</v>
+        <v>78.94</v>
       </c>
       <c r="D245" t="n">
-        <v>10689</v>
+        <v>23255</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>113.36</v>
+        <v>91.48</v>
       </c>
       <c r="B246" t="n">
-        <v>24221</v>
+        <v>20914</v>
       </c>
       <c r="C246" t="n">
-        <v>116.01</v>
+        <v>86.23</v>
       </c>
       <c r="D246" t="n">
-        <v>27691</v>
+        <v>22767</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>141.27</v>
+        <v>91.75</v>
       </c>
       <c r="B247" t="n">
-        <v>20962</v>
+        <v>22107</v>
       </c>
       <c r="C247" t="n">
-        <v>146.13</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="D247" t="n">
-        <v>12915</v>
+        <v>13603</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>35.59</v>
+        <v>92.34</v>
       </c>
       <c r="B248" t="n">
-        <v>23649</v>
+        <v>21944</v>
       </c>
       <c r="C248" t="n">
-        <v>36.23</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D248" t="n">
-        <v>10543</v>
+        <v>19231</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>98.18000000000001</v>
+        <v>92.42</v>
       </c>
       <c r="B249" t="n">
-        <v>39681</v>
+        <v>21755</v>
       </c>
       <c r="C249" t="n">
-        <v>99.69</v>
+        <v>73.31</v>
       </c>
       <c r="D249" t="n">
-        <v>24367</v>
+        <v>24739</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>111.18</v>
+        <v>92.45</v>
       </c>
       <c r="B250" t="n">
-        <v>29631</v>
+        <v>21840</v>
       </c>
       <c r="C250" t="n">
-        <v>111.26</v>
+        <v>91.23</v>
       </c>
       <c r="D250" t="n">
-        <v>15713</v>
+        <v>17398</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>108.32</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="B251" t="n">
-        <v>38255</v>
+        <v>22500</v>
       </c>
       <c r="C251" t="n">
-        <v>108.02</v>
+        <v>88.25</v>
       </c>
       <c r="D251" t="n">
-        <v>20392</v>
+        <v>13161</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>93.72</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="B252" t="n">
-        <v>30810</v>
+        <v>24400</v>
       </c>
       <c r="C252" t="n">
-        <v>94.22</v>
+        <v>105.65</v>
       </c>
       <c r="D252" t="n">
-        <v>11717</v>
+        <v>13804</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>108.03</v>
+        <v>93.59</v>
       </c>
       <c r="B253" t="n">
-        <v>38296</v>
+        <v>23368</v>
       </c>
       <c r="C253" t="n">
-        <v>111.16</v>
+        <v>98.73</v>
       </c>
       <c r="D253" t="n">
-        <v>27792</v>
+        <v>14653</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>98.81999999999999</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="B254" t="n">
-        <v>43196</v>
+        <v>25573</v>
       </c>
       <c r="C254" t="n">
-        <v>94.69</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="D254" t="n">
-        <v>26636</v>
+        <v>16999</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>101.51</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="B255" t="n">
-        <v>49639</v>
+        <v>25150</v>
       </c>
       <c r="C255" t="n">
-        <v>100.85</v>
+        <v>110.47</v>
       </c>
       <c r="D255" t="n">
-        <v>21966</v>
+        <v>11518</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>95.09999999999999</v>
+        <v>95.53</v>
       </c>
       <c r="B256" t="n">
-        <v>33944</v>
+        <v>26129</v>
       </c>
       <c r="C256" t="n">
-        <v>92.27</v>
+        <v>76.48</v>
       </c>
       <c r="D256" t="n">
-        <v>10683</v>
+        <v>12007</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>102.67</v>
+        <v>95.69</v>
       </c>
       <c r="B257" t="n">
-        <v>45343</v>
+        <v>25639</v>
       </c>
       <c r="C257" t="n">
-        <v>106.36</v>
+        <v>106.18</v>
       </c>
       <c r="D257" t="n">
-        <v>17994</v>
+        <v>19283</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>111.2</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="B258" t="n">
-        <v>31046</v>
+        <v>26591</v>
       </c>
       <c r="C258" t="n">
-        <v>115.85</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="D258" t="n">
-        <v>22281</v>
+        <v>28957</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>112.73</v>
+        <v>96.59</v>
       </c>
       <c r="B259" t="n">
-        <v>26007</v>
+        <v>27834</v>
       </c>
       <c r="C259" t="n">
-        <v>112.06</v>
+        <v>112.49</v>
       </c>
       <c r="D259" t="n">
-        <v>13695</v>
+        <v>13665</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>17.86</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="B260" t="n">
-        <v>23580</v>
+        <v>28434</v>
       </c>
       <c r="C260" t="n">
-        <v>18.55</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="D260" t="n">
-        <v>14066</v>
+        <v>11199</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>111.8</v>
+        <v>96.8</v>
       </c>
       <c r="B261" t="n">
-        <v>25790</v>
+        <v>27968</v>
       </c>
       <c r="C261" t="n">
-        <v>114.56</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="D261" t="n">
-        <v>24128</v>
+        <v>13484</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>112.58</v>
+        <v>97.04000000000001</v>
       </c>
       <c r="B262" t="n">
-        <v>27010</v>
+        <v>28458</v>
       </c>
       <c r="C262" t="n">
-        <v>112.84</v>
+        <v>116.03</v>
       </c>
       <c r="D262" t="n">
-        <v>16273</v>
+        <v>29807</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>107.31</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="B263" t="n">
-        <v>41712</v>
+        <v>31914</v>
       </c>
       <c r="C263" t="n">
-        <v>104.1</v>
+        <v>84.5</v>
       </c>
       <c r="D263" t="n">
-        <v>10651</v>
+        <v>25969</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>103.03</v>
+        <v>98.69</v>
       </c>
       <c r="B264" t="n">
-        <v>47598</v>
+        <v>32838</v>
       </c>
       <c r="C264" t="n">
-        <v>102.08</v>
+        <v>101</v>
       </c>
       <c r="D264" t="n">
-        <v>22556</v>
+        <v>21746</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>98.68000000000001</v>
+        <v>98.75</v>
       </c>
       <c r="B265" t="n">
-        <v>41005</v>
+        <v>32180</v>
       </c>
       <c r="C265" t="n">
-        <v>100.43</v>
+        <v>106</v>
       </c>
       <c r="D265" t="n">
-        <v>19218</v>
+        <v>29688</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>108.19</v>
+        <v>98.92</v>
       </c>
       <c r="B266" t="n">
-        <v>37290</v>
+        <v>32970</v>
       </c>
       <c r="C266" t="n">
-        <v>104.28</v>
+        <v>109.44</v>
       </c>
       <c r="D266" t="n">
-        <v>17548</v>
+        <v>11405</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>110.81</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="B267" t="n">
-        <v>31699</v>
+        <v>34831</v>
       </c>
       <c r="C267" t="n">
-        <v>111.3</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="D267" t="n">
-        <v>14285</v>
+        <v>27680</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>92.93000000000001</v>
+        <v>99.87</v>
       </c>
       <c r="B268" t="n">
-        <v>27523</v>
+        <v>34682</v>
       </c>
       <c r="C268" t="n">
-        <v>92.64</v>
+        <v>107.19</v>
       </c>
       <c r="D268" t="n">
-        <v>23867</v>
+        <v>17956</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>93.59</v>
+        <v>100.12</v>
       </c>
       <c r="B269" t="n">
-        <v>28597</v>
+        <v>34407</v>
       </c>
       <c r="C269" t="n">
-        <v>95.76000000000001</v>
+        <v>98.02</v>
       </c>
       <c r="D269" t="n">
-        <v>26977</v>
+        <v>22058</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>3.15</v>
+        <v>100.19</v>
       </c>
       <c r="B270" t="n">
-        <v>19571</v>
+        <v>35234</v>
       </c>
       <c r="C270" t="n">
-        <v>3.44</v>
+        <v>122.36</v>
       </c>
       <c r="D270" t="n">
-        <v>25134</v>
+        <v>12403</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>92.08</v>
+        <v>100.45</v>
       </c>
       <c r="B271" t="n">
-        <v>25826</v>
+        <v>35508</v>
       </c>
       <c r="C271" t="n">
-        <v>94.95999999999999</v>
+        <v>85.75</v>
       </c>
       <c r="D271" t="n">
-        <v>16833</v>
+        <v>25543</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>113.96</v>
+        <v>101.86</v>
       </c>
       <c r="B272" t="n">
-        <v>27677</v>
+        <v>37843</v>
       </c>
       <c r="C272" t="n">
-        <v>112.54</v>
+        <v>108.52</v>
       </c>
       <c r="D272" t="n">
-        <v>21036</v>
+        <v>23323</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>102.33</v>
+        <v>102.05</v>
       </c>
       <c r="B273" t="n">
-        <v>47140</v>
+        <v>38291</v>
       </c>
       <c r="C273" t="n">
-        <v>98.23</v>
+        <v>108.56</v>
       </c>
       <c r="D273" t="n">
-        <v>17947</v>
+        <v>15081</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>95.36</v>
+        <v>102.16</v>
       </c>
       <c r="B274" t="n">
-        <v>33863</v>
+        <v>37583</v>
       </c>
       <c r="C274" t="n">
-        <v>97.75</v>
+        <v>102.36</v>
       </c>
       <c r="D274" t="n">
-        <v>28217</v>
+        <v>18816</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>174.36</v>
+        <v>102.45</v>
       </c>
       <c r="B275" t="n">
-        <v>21358</v>
+        <v>37553</v>
       </c>
       <c r="C275" t="n">
-        <v>175.01</v>
+        <v>96.23</v>
       </c>
       <c r="D275" t="n">
-        <v>29528</v>
+        <v>16293</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>50.72</v>
+        <v>102.56</v>
       </c>
       <c r="B276" t="n">
-        <v>24357</v>
+        <v>37714</v>
       </c>
       <c r="C276" t="n">
-        <v>49.86</v>
+        <v>103.32</v>
       </c>
       <c r="D276" t="n">
-        <v>19858</v>
+        <v>16108</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>106.61</v>
+        <v>102.72</v>
       </c>
       <c r="B277" t="n">
-        <v>41436</v>
+        <v>38298</v>
       </c>
       <c r="C277" t="n">
-        <v>101.34</v>
+        <v>94.39</v>
       </c>
       <c r="D277" t="n">
-        <v>10641</v>
+        <v>25842</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>73.94</v>
+        <v>103.1</v>
       </c>
       <c r="B278" t="n">
-        <v>23826</v>
+        <v>38204</v>
       </c>
       <c r="C278" t="n">
-        <v>72.77</v>
+        <v>96.77</v>
       </c>
       <c r="D278" t="n">
-        <v>26551</v>
+        <v>14319</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>102.24</v>
+        <v>103.91</v>
       </c>
       <c r="B279" t="n">
-        <v>46066</v>
+        <v>37234</v>
       </c>
       <c r="C279" t="n">
-        <v>103.01</v>
+        <v>120.54</v>
       </c>
       <c r="D279" t="n">
-        <v>25104</v>
+        <v>28635</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>90.77</v>
+        <v>104.15</v>
       </c>
       <c r="B280" t="n">
-        <v>22695</v>
+        <v>36900</v>
       </c>
       <c r="C280" t="n">
-        <v>88.36</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="D280" t="n">
-        <v>22051</v>
+        <v>12729</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>104.31</v>
+        <v>104.29</v>
       </c>
       <c r="B281" t="n">
-        <v>44996</v>
+        <v>37832</v>
       </c>
       <c r="C281" t="n">
-        <v>108.09</v>
+        <v>123.5</v>
       </c>
       <c r="D281" t="n">
-        <v>16774</v>
+        <v>16426</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>108.8</v>
+        <v>104.5</v>
       </c>
       <c r="B282" t="n">
-        <v>36855</v>
+        <v>37493</v>
       </c>
       <c r="C282" t="n">
-        <v>110.77</v>
+        <v>131.08</v>
       </c>
       <c r="D282" t="n">
-        <v>15998</v>
+        <v>28896</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>74.93000000000001</v>
+        <v>104.97</v>
       </c>
       <c r="B283" t="n">
-        <v>25503</v>
+        <v>37266</v>
       </c>
       <c r="C283" t="n">
-        <v>75.65000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="D283" t="n">
-        <v>27981</v>
+        <v>26837</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>65.15000000000001</v>
+        <v>105.19</v>
       </c>
       <c r="B284" t="n">
-        <v>23683</v>
+        <v>35512</v>
       </c>
       <c r="C284" t="n">
-        <v>65.63</v>
+        <v>109.53</v>
       </c>
       <c r="D284" t="n">
-        <v>15787</v>
+        <v>27777</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>104.79</v>
+        <v>105.42</v>
       </c>
       <c r="B285" t="n">
-        <v>44415</v>
+        <v>36810</v>
       </c>
       <c r="C285" t="n">
-        <v>100.72</v>
+        <v>109.17</v>
       </c>
       <c r="D285" t="n">
-        <v>10963</v>
+        <v>24634</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>113.19</v>
+        <v>105.51</v>
       </c>
       <c r="B286" t="n">
-        <v>24898</v>
+        <v>35555</v>
       </c>
       <c r="C286" t="n">
-        <v>114.08</v>
+        <v>97.25</v>
       </c>
       <c r="D286" t="n">
-        <v>17018</v>
+        <v>14202</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>98.33</v>
+        <v>105.65</v>
       </c>
       <c r="B287" t="n">
-        <v>42247</v>
+        <v>36492</v>
       </c>
       <c r="C287" t="n">
-        <v>96.2</v>
+        <v>117.88</v>
       </c>
       <c r="D287" t="n">
-        <v>20661</v>
+        <v>27724</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>151.99</v>
+        <v>106.22</v>
       </c>
       <c r="B288" t="n">
-        <v>20277</v>
+        <v>33880</v>
       </c>
       <c r="C288" t="n">
-        <v>157.66</v>
+        <v>125.23</v>
       </c>
       <c r="D288" t="n">
-        <v>18488</v>
+        <v>10653</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>59.05</v>
+        <v>106.25</v>
       </c>
       <c r="B289" t="n">
-        <v>22303</v>
+        <v>34257</v>
       </c>
       <c r="C289" t="n">
-        <v>60.89</v>
+        <v>96.23</v>
       </c>
       <c r="D289" t="n">
-        <v>11353</v>
+        <v>19727</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>112.94</v>
+        <v>106.26</v>
       </c>
       <c r="B290" t="n">
-        <v>27961</v>
+        <v>34486</v>
       </c>
       <c r="C290" t="n">
-        <v>112.73</v>
+        <v>113.87</v>
       </c>
       <c r="D290" t="n">
-        <v>16599</v>
+        <v>23999</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>98.06999999999999</v>
+        <v>106.5</v>
       </c>
       <c r="B291" t="n">
-        <v>41183</v>
+        <v>33663</v>
       </c>
       <c r="C291" t="n">
-        <v>100.09</v>
+        <v>116.32</v>
       </c>
       <c r="D291" t="n">
-        <v>22791</v>
+        <v>21227</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>102.57</v>
+        <v>106.81</v>
       </c>
       <c r="B292" t="n">
-        <v>47800</v>
+        <v>32128</v>
       </c>
       <c r="C292" t="n">
-        <v>102.31</v>
+        <v>101.79</v>
       </c>
       <c r="D292" t="n">
-        <v>29490</v>
+        <v>21294</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>104.78</v>
+        <v>108.03</v>
       </c>
       <c r="B293" t="n">
-        <v>45429</v>
+        <v>30503</v>
       </c>
       <c r="C293" t="n">
-        <v>104.43</v>
+        <v>134.49</v>
       </c>
       <c r="D293" t="n">
-        <v>24348</v>
+        <v>19689</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>110.17</v>
+        <v>109.01</v>
       </c>
       <c r="B294" t="n">
-        <v>30611</v>
+        <v>27545</v>
       </c>
       <c r="C294" t="n">
-        <v>108.79</v>
+        <v>90.92</v>
       </c>
       <c r="D294" t="n">
-        <v>26458</v>
+        <v>27549</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>90.56</v>
+        <v>109.1</v>
       </c>
       <c r="B295" t="n">
-        <v>23167</v>
+        <v>29921</v>
       </c>
       <c r="C295" t="n">
-        <v>91.76000000000001</v>
+        <v>115.01</v>
       </c>
       <c r="D295" t="n">
-        <v>28364</v>
+        <v>29712</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>99.06999999999999</v>
+        <v>109.2</v>
       </c>
       <c r="B296" t="n">
-        <v>45089</v>
+        <v>27457</v>
       </c>
       <c r="C296" t="n">
-        <v>100.02</v>
+        <v>117.49</v>
       </c>
       <c r="D296" t="n">
-        <v>27024</v>
+        <v>18168</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>111.17</v>
+        <v>109.28</v>
       </c>
       <c r="B297" t="n">
-        <v>27882</v>
+        <v>27063</v>
       </c>
       <c r="C297" t="n">
-        <v>115.42</v>
+        <v>118.93</v>
       </c>
       <c r="D297" t="n">
-        <v>10981</v>
+        <v>12480</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>99.52</v>
+        <v>109.51</v>
       </c>
       <c r="B298" t="n">
-        <v>43523</v>
+        <v>28016</v>
       </c>
       <c r="C298" t="n">
-        <v>99.72</v>
+        <v>103.77</v>
       </c>
       <c r="D298" t="n">
-        <v>20384</v>
+        <v>27389</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>113.49</v>
+        <v>109.78</v>
       </c>
       <c r="B299" t="n">
-        <v>22743</v>
+        <v>27104</v>
       </c>
       <c r="C299" t="n">
-        <v>112.7</v>
+        <v>126.74</v>
       </c>
       <c r="D299" t="n">
-        <v>23973</v>
+        <v>11708</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>100.02</v>
+        <v>109.81</v>
       </c>
       <c r="B300" t="n">
-        <v>45184</v>
+        <v>27527</v>
       </c>
       <c r="C300" t="n">
-        <v>100.51</v>
+        <v>120.78</v>
       </c>
       <c r="D300" t="n">
-        <v>16092</v>
+        <v>22101</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>94.3</v>
+        <v>110.27</v>
       </c>
       <c r="B301" t="n">
-        <v>32903</v>
+        <v>25958</v>
       </c>
       <c r="C301" t="n">
-        <v>92.78</v>
+        <v>111.26</v>
       </c>
       <c r="D301" t="n">
-        <v>23441</v>
+        <v>16601</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>96.73999999999999</v>
+        <v>110.58</v>
       </c>
       <c r="B302" t="n">
-        <v>37611</v>
+        <v>24620</v>
       </c>
       <c r="C302" t="n">
-        <v>94.52</v>
+        <v>101.28</v>
       </c>
       <c r="D302" t="n">
-        <v>22282</v>
+        <v>15135</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>80.34999999999999</v>
+        <v>110.97</v>
       </c>
       <c r="B303" t="n">
-        <v>27246</v>
+        <v>24205</v>
       </c>
       <c r="C303" t="n">
-        <v>81.16</v>
+        <v>118.62</v>
       </c>
       <c r="D303" t="n">
-        <v>23716</v>
+        <v>21199</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>107.11</v>
+        <v>111.02</v>
       </c>
       <c r="B304" t="n">
-        <v>42292</v>
+        <v>25781</v>
       </c>
       <c r="C304" t="n">
-        <v>103.48</v>
+        <v>120.93</v>
       </c>
       <c r="D304" t="n">
-        <v>24327</v>
+        <v>27044</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>103.24</v>
+        <v>111.28</v>
       </c>
       <c r="B305" t="n">
-        <v>45435</v>
+        <v>23176</v>
       </c>
       <c r="C305" t="n">
-        <v>102.33</v>
+        <v>85.08</v>
       </c>
       <c r="D305" t="n">
-        <v>15957</v>
+        <v>27855</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>111.64</v>
+        <v>112.01</v>
       </c>
       <c r="B306" t="n">
-        <v>28273</v>
+        <v>21974</v>
       </c>
       <c r="C306" t="n">
-        <v>110.29</v>
+        <v>129.53</v>
       </c>
       <c r="D306" t="n">
-        <v>14055</v>
+        <v>21737</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>160.38</v>
+        <v>112.12</v>
       </c>
       <c r="B307" t="n">
-        <v>22445</v>
+        <v>23018</v>
       </c>
       <c r="C307" t="n">
-        <v>163</v>
+        <v>105.84</v>
       </c>
       <c r="D307" t="n">
-        <v>17647</v>
+        <v>18044</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>110.42</v>
+        <v>112.33</v>
       </c>
       <c r="B308" t="n">
-        <v>30398</v>
+        <v>22604</v>
       </c>
       <c r="C308" t="n">
-        <v>106.31</v>
+        <v>104.63</v>
       </c>
       <c r="D308" t="n">
-        <v>10823</v>
+        <v>22121</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>91.25</v>
+        <v>112.5</v>
       </c>
       <c r="B309" t="n">
-        <v>21959</v>
+        <v>22836</v>
       </c>
       <c r="C309" t="n">
-        <v>90.86</v>
+        <v>130.16</v>
       </c>
       <c r="D309" t="n">
-        <v>15210</v>
+        <v>11974</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>97.97</v>
+        <v>113.51</v>
       </c>
       <c r="B310" t="n">
-        <v>40197</v>
+        <v>22078</v>
       </c>
       <c r="C310" t="n">
-        <v>100.77</v>
+        <v>101.18</v>
       </c>
       <c r="D310" t="n">
-        <v>12905</v>
+        <v>12380</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>124.02</v>
+        <v>113.71</v>
       </c>
       <c r="B311" t="n">
-        <v>26083</v>
+        <v>21269</v>
       </c>
       <c r="C311" t="n">
-        <v>126.26</v>
+        <v>115.94</v>
       </c>
       <c r="D311" t="n">
-        <v>14317</v>
+        <v>26579</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>99.81</v>
+        <v>113.72</v>
       </c>
       <c r="B312" t="n">
-        <v>43839</v>
+        <v>20691</v>
       </c>
       <c r="C312" t="n">
-        <v>102.53</v>
+        <v>136.63</v>
       </c>
       <c r="D312" t="n">
-        <v>29879</v>
+        <v>28282</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>100.41</v>
+        <v>113.76</v>
       </c>
       <c r="B313" t="n">
-        <v>49268</v>
+        <v>21596</v>
       </c>
       <c r="C313" t="n">
-        <v>98.58</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="D313" t="n">
-        <v>16822</v>
+        <v>16338</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>95.06999999999999</v>
+        <v>113.88</v>
       </c>
       <c r="B314" t="n">
-        <v>31150</v>
+        <v>21865</v>
       </c>
       <c r="C314" t="n">
-        <v>92.89</v>
+        <v>88.45</v>
       </c>
       <c r="D314" t="n">
-        <v>11532</v>
+        <v>14630</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>75.87</v>
+        <v>114.1</v>
       </c>
       <c r="B315" t="n">
-        <v>24452</v>
+        <v>22375</v>
       </c>
       <c r="C315" t="n">
-        <v>74.69</v>
+        <v>103.24</v>
       </c>
       <c r="D315" t="n">
-        <v>23153</v>
+        <v>17354</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>104.4</v>
+        <v>114.39</v>
       </c>
       <c r="B316" t="n">
-        <v>47495</v>
+        <v>20832</v>
       </c>
       <c r="C316" t="n">
-        <v>101.74</v>
+        <v>138.8</v>
       </c>
       <c r="D316" t="n">
-        <v>16484</v>
+        <v>19356</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>94.90000000000001</v>
+        <v>114.95</v>
       </c>
       <c r="B317" t="n">
-        <v>33160</v>
+        <v>20814</v>
       </c>
       <c r="C317" t="n">
-        <v>98.38</v>
+        <v>117.49</v>
       </c>
       <c r="D317" t="n">
-        <v>23806</v>
+        <v>26054</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>98.69</v>
+        <v>115.18</v>
       </c>
       <c r="B318" t="n">
-        <v>40948</v>
+        <v>19952</v>
       </c>
       <c r="C318" t="n">
-        <v>95.91</v>
+        <v>93.13</v>
       </c>
       <c r="D318" t="n">
-        <v>19158</v>
+        <v>27728</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>94.62</v>
+        <v>115.4</v>
       </c>
       <c r="B319" t="n">
-        <v>29041</v>
+        <v>21005</v>
       </c>
       <c r="C319" t="n">
-        <v>95.03</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="D319" t="n">
-        <v>18215</v>
+        <v>20529</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>0.08</v>
+        <v>115.77</v>
       </c>
       <c r="B320" t="n">
-        <v>24717</v>
+        <v>20628</v>
       </c>
       <c r="C320" t="n">
-        <v>0</v>
+        <v>115.79</v>
       </c>
       <c r="D320" t="n">
-        <v>25022</v>
+        <v>22658</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>96.12</v>
+        <v>115.81</v>
       </c>
       <c r="B321" t="n">
-        <v>33955</v>
+        <v>20057</v>
       </c>
       <c r="C321" t="n">
-        <v>97.89</v>
+        <v>125.71</v>
       </c>
       <c r="D321" t="n">
-        <v>12292</v>
+        <v>20056</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>114.63</v>
+        <v>116.48</v>
       </c>
       <c r="B322" t="n">
-        <v>26233</v>
+        <v>19349</v>
       </c>
       <c r="C322" t="n">
-        <v>117.44</v>
+        <v>125.54</v>
       </c>
       <c r="D322" t="n">
-        <v>12428</v>
+        <v>16094</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>110.85</v>
+        <v>116.69</v>
       </c>
       <c r="B323" t="n">
-        <v>29989</v>
+        <v>19490</v>
       </c>
       <c r="C323" t="n">
-        <v>108.09</v>
+        <v>114.48</v>
       </c>
       <c r="D323" t="n">
-        <v>22325</v>
+        <v>26229</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>110.29</v>
+        <v>116.69</v>
       </c>
       <c r="B324" t="n">
-        <v>30158</v>
+        <v>21457</v>
       </c>
       <c r="C324" t="n">
-        <v>108.29</v>
+        <v>114.87</v>
       </c>
       <c r="D324" t="n">
-        <v>24535</v>
+        <v>11080</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>90.61</v>
+        <v>116.78</v>
       </c>
       <c r="B325" t="n">
-        <v>22860</v>
+        <v>20309</v>
       </c>
       <c r="C325" t="n">
-        <v>92.36</v>
+        <v>127.71</v>
       </c>
       <c r="D325" t="n">
-        <v>20781</v>
+        <v>29318</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>137.44</v>
+        <v>117.07</v>
       </c>
       <c r="B326" t="n">
-        <v>19730</v>
+        <v>20867</v>
       </c>
       <c r="C326" t="n">
-        <v>137.17</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="D326" t="n">
-        <v>25039</v>
+        <v>21954</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>93.13</v>
+        <v>118.64</v>
       </c>
       <c r="B327" t="n">
-        <v>29306</v>
+        <v>19559</v>
       </c>
       <c r="C327" t="n">
-        <v>89.06</v>
+        <v>135.21</v>
       </c>
       <c r="D327" t="n">
-        <v>25958</v>
+        <v>28951</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>86.09999999999999</v>
+        <v>118.91</v>
       </c>
       <c r="B328" t="n">
-        <v>23008</v>
+        <v>19793</v>
       </c>
       <c r="C328" t="n">
-        <v>87.90000000000001</v>
+        <v>112.33</v>
       </c>
       <c r="D328" t="n">
-        <v>19241</v>
+        <v>13901</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>104.9</v>
+        <v>118.94</v>
       </c>
       <c r="B329" t="n">
-        <v>44951</v>
+        <v>19482</v>
       </c>
       <c r="C329" t="n">
-        <v>105.32</v>
+        <v>121.88</v>
       </c>
       <c r="D329" t="n">
-        <v>13637</v>
+        <v>28147</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>100.05</v>
+        <v>119.17</v>
       </c>
       <c r="B330" t="n">
-        <v>46017</v>
+        <v>20498</v>
       </c>
       <c r="C330" t="n">
-        <v>97.94</v>
+        <v>133.11</v>
       </c>
       <c r="D330" t="n">
-        <v>27268</v>
+        <v>29087</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>143.24</v>
+        <v>119.89</v>
       </c>
       <c r="B331" t="n">
-        <v>24337</v>
+        <v>20154</v>
       </c>
       <c r="C331" t="n">
-        <v>144.79</v>
+        <v>131.19</v>
       </c>
       <c r="D331" t="n">
-        <v>23188</v>
+        <v>17889</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>112.08</v>
+        <v>120.03</v>
       </c>
       <c r="B332" t="n">
-        <v>28902</v>
+        <v>19842</v>
       </c>
       <c r="C332" t="n">
-        <v>114.35</v>
+        <v>101.6</v>
       </c>
       <c r="D332" t="n">
-        <v>24266</v>
+        <v>16544</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>101.36</v>
+        <v>120.39</v>
       </c>
       <c r="B333" t="n">
-        <v>48408</v>
+        <v>18729</v>
       </c>
       <c r="C333" t="n">
-        <v>103.91</v>
+        <v>136.73</v>
       </c>
       <c r="D333" t="n">
-        <v>22284</v>
+        <v>19975</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>107.96</v>
+        <v>120.55</v>
       </c>
       <c r="B334" t="n">
-        <v>36166</v>
+        <v>18548</v>
       </c>
       <c r="C334" t="n">
-        <v>108.66</v>
+        <v>124.32</v>
       </c>
       <c r="D334" t="n">
-        <v>13127</v>
+        <v>29547</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>96.89</v>
+        <v>120.9</v>
       </c>
       <c r="B335" t="n">
-        <v>38248</v>
+        <v>20319</v>
       </c>
       <c r="C335" t="n">
-        <v>94.56</v>
+        <v>107.76</v>
       </c>
       <c r="D335" t="n">
-        <v>18322</v>
+        <v>13764</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>95.15000000000001</v>
+        <v>122.21</v>
       </c>
       <c r="B336" t="n">
-        <v>35274</v>
+        <v>20444</v>
       </c>
       <c r="C336" t="n">
-        <v>92.53</v>
+        <v>118.16</v>
       </c>
       <c r="D336" t="n">
-        <v>28853</v>
+        <v>14449</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>145.69</v>
+        <v>122.6</v>
       </c>
       <c r="B337" t="n">
-        <v>21936</v>
+        <v>20675</v>
       </c>
       <c r="C337" t="n">
-        <v>150.52</v>
+        <v>121.3</v>
       </c>
       <c r="D337" t="n">
-        <v>12021</v>
+        <v>11542</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>94.26000000000001</v>
+        <v>122.69</v>
       </c>
       <c r="B338" t="n">
-        <v>28778</v>
+        <v>19980</v>
       </c>
       <c r="C338" t="n">
-        <v>94.44</v>
+        <v>116.3</v>
       </c>
       <c r="D338" t="n">
-        <v>23284</v>
+        <v>14539</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>77.51000000000001</v>
+        <v>122.98</v>
       </c>
       <c r="B339" t="n">
-        <v>20466</v>
+        <v>19720</v>
       </c>
       <c r="C339" t="n">
-        <v>78.06</v>
+        <v>127.18</v>
       </c>
       <c r="D339" t="n">
-        <v>25310</v>
+        <v>18863</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>111.15</v>
+        <v>123.36</v>
       </c>
       <c r="B340" t="n">
-        <v>27032</v>
+        <v>19667</v>
       </c>
       <c r="C340" t="n">
-        <v>109.88</v>
+        <v>136.98</v>
       </c>
       <c r="D340" t="n">
-        <v>12213</v>
+        <v>20251</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>109.36</v>
+        <v>123.75</v>
       </c>
       <c r="B341" t="n">
-        <v>34263</v>
+        <v>19026</v>
       </c>
       <c r="C341" t="n">
-        <v>106.55</v>
+        <v>135.47</v>
       </c>
       <c r="D341" t="n">
-        <v>14817</v>
+        <v>17052</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>94.15000000000001</v>
+        <v>123.86</v>
       </c>
       <c r="B342" t="n">
-        <v>29973</v>
+        <v>19642</v>
       </c>
       <c r="C342" t="n">
-        <v>91.09</v>
+        <v>107</v>
       </c>
       <c r="D342" t="n">
-        <v>26897</v>
+        <v>10887</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>27.18</v>
+        <v>124.33</v>
       </c>
       <c r="B343" t="n">
-        <v>23555</v>
+        <v>18811</v>
       </c>
       <c r="C343" t="n">
-        <v>28.06</v>
+        <v>129.94</v>
       </c>
       <c r="D343" t="n">
-        <v>17949</v>
+        <v>25587</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>104.07</v>
+        <v>124.44</v>
       </c>
       <c r="B344" t="n">
-        <v>48442</v>
+        <v>19720</v>
       </c>
       <c r="C344" t="n">
-        <v>101.41</v>
+        <v>123.95</v>
       </c>
       <c r="D344" t="n">
-        <v>18881</v>
+        <v>22487</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>169.59</v>
+        <v>124.59</v>
       </c>
       <c r="B345" t="n">
-        <v>20981</v>
+        <v>18554</v>
       </c>
       <c r="C345" t="n">
-        <v>162.74</v>
+        <v>145.77</v>
       </c>
       <c r="D345" t="n">
-        <v>15765</v>
+        <v>18795</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>103.58</v>
+        <v>124.99</v>
       </c>
       <c r="B346" t="n">
-        <v>45982</v>
+        <v>21613</v>
       </c>
       <c r="C346" t="n">
-        <v>102.08</v>
+        <v>100.46</v>
       </c>
       <c r="D346" t="n">
-        <v>10630</v>
+        <v>18902</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>135.98</v>
+        <v>125.59</v>
       </c>
       <c r="B347" t="n">
-        <v>21470</v>
+        <v>17777</v>
       </c>
       <c r="C347" t="n">
-        <v>132.54</v>
+        <v>148.73</v>
       </c>
       <c r="D347" t="n">
-        <v>17356</v>
+        <v>13792</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>90.2</v>
+        <v>125.86</v>
       </c>
       <c r="B348" t="n">
-        <v>21909</v>
+        <v>20218</v>
       </c>
       <c r="C348" t="n">
-        <v>91.47</v>
+        <v>124.82</v>
       </c>
       <c r="D348" t="n">
-        <v>13477</v>
+        <v>25475</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>113.37</v>
+        <v>126.44</v>
       </c>
       <c r="B349" t="n">
-        <v>23625</v>
+        <v>19203</v>
       </c>
       <c r="C349" t="n">
-        <v>109.85</v>
+        <v>137.29</v>
       </c>
       <c r="D349" t="n">
-        <v>15485</v>
+        <v>23150</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>104.4</v>
+        <v>126.52</v>
       </c>
       <c r="B350" t="n">
-        <v>48222</v>
+        <v>19635</v>
       </c>
       <c r="C350" t="n">
-        <v>99.37</v>
+        <v>135.3</v>
       </c>
       <c r="D350" t="n">
-        <v>22967</v>
+        <v>22223</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>107.49</v>
+        <v>127.61</v>
       </c>
       <c r="B351" t="n">
-        <v>41286</v>
+        <v>19919</v>
       </c>
       <c r="C351" t="n">
-        <v>110.21</v>
+        <v>108.57</v>
       </c>
       <c r="D351" t="n">
-        <v>15796</v>
+        <v>15868</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>102.15</v>
+        <v>128.02</v>
       </c>
       <c r="B352" t="n">
-        <v>45927</v>
+        <v>16900</v>
       </c>
       <c r="C352" t="n">
-        <v>101.72</v>
+        <v>113.46</v>
       </c>
       <c r="D352" t="n">
-        <v>19004</v>
+        <v>15051</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>44.12</v>
+        <v>128.32</v>
       </c>
       <c r="B353" t="n">
-        <v>24475</v>
+        <v>20581</v>
       </c>
       <c r="C353" t="n">
-        <v>45.45</v>
+        <v>128.55</v>
       </c>
       <c r="D353" t="n">
-        <v>15184</v>
+        <v>27167</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>102.8</v>
+        <v>128.39</v>
       </c>
       <c r="B354" t="n">
-        <v>47723</v>
+        <v>17404</v>
       </c>
       <c r="C354" t="n">
-        <v>102.61</v>
+        <v>124.3</v>
       </c>
       <c r="D354" t="n">
-        <v>28222</v>
+        <v>25717</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>94.33</v>
+        <v>128.55</v>
       </c>
       <c r="B355" t="n">
-        <v>32497</v>
+        <v>20232</v>
       </c>
       <c r="C355" t="n">
-        <v>95.18000000000001</v>
+        <v>110.85</v>
       </c>
       <c r="D355" t="n">
-        <v>11875</v>
+        <v>20069</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>86.23</v>
+        <v>129.71</v>
       </c>
       <c r="B356" t="n">
-        <v>24717</v>
+        <v>17337</v>
       </c>
       <c r="C356" t="n">
-        <v>86.64</v>
+        <v>129.24</v>
       </c>
       <c r="D356" t="n">
-        <v>12908</v>
+        <v>18229</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>97.43000000000001</v>
+        <v>130.01</v>
       </c>
       <c r="B357" t="n">
-        <v>36938</v>
+        <v>19058</v>
       </c>
       <c r="C357" t="n">
-        <v>99.59999999999999</v>
+        <v>152.32</v>
       </c>
       <c r="D357" t="n">
-        <v>13813</v>
+        <v>23550</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>103.01</v>
+        <v>130.02</v>
       </c>
       <c r="B358" t="n">
-        <v>45997</v>
+        <v>19718</v>
       </c>
       <c r="C358" t="n">
-        <v>106.8</v>
+        <v>121.48</v>
       </c>
       <c r="D358" t="n">
-        <v>13757</v>
+        <v>17264</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>111.04</v>
+        <v>130.05</v>
       </c>
       <c r="B359" t="n">
-        <v>30319</v>
+        <v>17766</v>
       </c>
       <c r="C359" t="n">
-        <v>110.49</v>
+        <v>108.9</v>
       </c>
       <c r="D359" t="n">
-        <v>18971</v>
+        <v>25026</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>109</v>
+        <v>130.11</v>
       </c>
       <c r="B360" t="n">
-        <v>34606</v>
+        <v>18206</v>
       </c>
       <c r="C360" t="n">
-        <v>105.26</v>
+        <v>140.29</v>
       </c>
       <c r="D360" t="n">
-        <v>18211</v>
+        <v>18381</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>91.89</v>
+        <v>130.39</v>
       </c>
       <c r="B361" t="n">
-        <v>26043</v>
+        <v>18659</v>
       </c>
       <c r="C361" t="n">
-        <v>94.90000000000001</v>
+        <v>109.06</v>
       </c>
       <c r="D361" t="n">
-        <v>28506</v>
+        <v>24994</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>107.67</v>
+        <v>130.76</v>
       </c>
       <c r="B362" t="n">
-        <v>37700</v>
+        <v>20335</v>
       </c>
       <c r="C362" t="n">
-        <v>105.3</v>
+        <v>120.12</v>
       </c>
       <c r="D362" t="n">
-        <v>15828</v>
+        <v>15079</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>90.77</v>
+        <v>131.8</v>
       </c>
       <c r="B363" t="n">
-        <v>27290</v>
+        <v>18850</v>
       </c>
       <c r="C363" t="n">
-        <v>91.31</v>
+        <v>150.65</v>
       </c>
       <c r="D363" t="n">
-        <v>19667</v>
+        <v>16477</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>108.32</v>
+        <v>132.49</v>
       </c>
       <c r="B364" t="n">
-        <v>36897</v>
+        <v>17754</v>
       </c>
       <c r="C364" t="n">
-        <v>112.24</v>
+        <v>122.5</v>
       </c>
       <c r="D364" t="n">
-        <v>29682</v>
+        <v>18090</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>112.71</v>
+        <v>132.56</v>
       </c>
       <c r="B365" t="n">
-        <v>26674</v>
+        <v>20209</v>
       </c>
       <c r="C365" t="n">
-        <v>110.24</v>
+        <v>133.72</v>
       </c>
       <c r="D365" t="n">
-        <v>14533</v>
+        <v>24170</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>109.07</v>
+        <v>132.72</v>
       </c>
       <c r="B366" t="n">
-        <v>33986</v>
+        <v>21190</v>
       </c>
       <c r="C366" t="n">
-        <v>109.85</v>
+        <v>158.23</v>
       </c>
       <c r="D366" t="n">
-        <v>26774</v>
+        <v>12859</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>5.75</v>
+        <v>132.85</v>
       </c>
       <c r="B367" t="n">
-        <v>22114</v>
+        <v>18774</v>
       </c>
       <c r="C367" t="n">
-        <v>4.87</v>
+        <v>144.26</v>
       </c>
       <c r="D367" t="n">
-        <v>17764</v>
+        <v>26587</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>113.56</v>
+        <v>132.92</v>
       </c>
       <c r="B368" t="n">
-        <v>22949</v>
+        <v>19188</v>
       </c>
       <c r="C368" t="n">
-        <v>112.08</v>
+        <v>118.69</v>
       </c>
       <c r="D368" t="n">
-        <v>14197</v>
+        <v>23277</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>112.32</v>
+        <v>133.03</v>
       </c>
       <c r="B369" t="n">
-        <v>28945</v>
+        <v>20742</v>
       </c>
       <c r="C369" t="n">
-        <v>110.22</v>
+        <v>120.21</v>
       </c>
       <c r="D369" t="n">
-        <v>20393</v>
+        <v>18843</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>100.52</v>
+        <v>133.29</v>
       </c>
       <c r="B370" t="n">
-        <v>44231</v>
+        <v>18885</v>
       </c>
       <c r="C370" t="n">
-        <v>98.28</v>
+        <v>136.59</v>
       </c>
       <c r="D370" t="n">
-        <v>25960</v>
+        <v>19897</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>94.14</v>
+        <v>133.59</v>
       </c>
       <c r="B371" t="n">
-        <v>31050</v>
+        <v>19169</v>
       </c>
       <c r="C371" t="n">
-        <v>95.75</v>
+        <v>127.41</v>
       </c>
       <c r="D371" t="n">
-        <v>21753</v>
+        <v>23633</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>135.79</v>
+        <v>133.65</v>
       </c>
       <c r="B372" t="n">
-        <v>21847</v>
+        <v>19349</v>
       </c>
       <c r="C372" t="n">
-        <v>131.51</v>
+        <v>136.5</v>
       </c>
       <c r="D372" t="n">
-        <v>16712</v>
+        <v>15499</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>90.92</v>
+        <v>133.66</v>
       </c>
       <c r="B373" t="n">
-        <v>21861</v>
+        <v>16216</v>
       </c>
       <c r="C373" t="n">
-        <v>94.91</v>
+        <v>133.07</v>
       </c>
       <c r="D373" t="n">
-        <v>11485</v>
+        <v>16406</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>93.27</v>
+        <v>133.68</v>
       </c>
       <c r="B374" t="n">
-        <v>27658</v>
+        <v>20003</v>
       </c>
       <c r="C374" t="n">
-        <v>92.78</v>
+        <v>137.59</v>
       </c>
       <c r="D374" t="n">
-        <v>15014</v>
+        <v>13675</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>98.40000000000001</v>
+        <v>133.69</v>
       </c>
       <c r="B375" t="n">
-        <v>41682</v>
+        <v>19682</v>
       </c>
       <c r="C375" t="n">
-        <v>101.62</v>
+        <v>133.53</v>
       </c>
       <c r="D375" t="n">
-        <v>15254</v>
+        <v>17477</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>92.29000000000001</v>
+        <v>133.69</v>
       </c>
       <c r="B376" t="n">
-        <v>27493</v>
+        <v>18470</v>
       </c>
       <c r="C376" t="n">
-        <v>90.59999999999999</v>
+        <v>122.22</v>
       </c>
       <c r="D376" t="n">
-        <v>27057</v>
+        <v>18141</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>178.3</v>
+        <v>134.08</v>
       </c>
       <c r="B377" t="n">
-        <v>23710</v>
+        <v>19880</v>
       </c>
       <c r="C377" t="n">
-        <v>171.73</v>
+        <v>134.44</v>
       </c>
       <c r="D377" t="n">
-        <v>16557</v>
+        <v>12385</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>109.36</v>
+        <v>134.15</v>
       </c>
       <c r="B378" t="n">
-        <v>35230</v>
+        <v>19197</v>
       </c>
       <c r="C378" t="n">
-        <v>107.01</v>
+        <v>124.49</v>
       </c>
       <c r="D378" t="n">
-        <v>20943</v>
+        <v>18877</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>101.73</v>
+        <v>134.54</v>
       </c>
       <c r="B379" t="n">
-        <v>47804</v>
+        <v>21496</v>
       </c>
       <c r="C379" t="n">
-        <v>101.84</v>
+        <v>130.03</v>
       </c>
       <c r="D379" t="n">
-        <v>11041</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>112.14</v>
+        <v>136.02</v>
       </c>
       <c r="B380" t="n">
-        <v>28257</v>
+        <v>17134</v>
       </c>
       <c r="C380" t="n">
-        <v>110.96</v>
+        <v>131.25</v>
       </c>
       <c r="D380" t="n">
-        <v>25444</v>
+        <v>26487</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>90.43000000000001</v>
+        <v>136.28</v>
       </c>
       <c r="B381" t="n">
-        <v>24144</v>
+        <v>19406</v>
       </c>
       <c r="C381" t="n">
-        <v>88.34999999999999</v>
+        <v>168.63</v>
       </c>
       <c r="D381" t="n">
-        <v>11175</v>
+        <v>19072</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>97.22</v>
+        <v>136.75</v>
       </c>
       <c r="B382" t="n">
-        <v>43018</v>
+        <v>18922</v>
       </c>
       <c r="C382" t="n">
-        <v>95.95</v>
+        <v>114.64</v>
       </c>
       <c r="D382" t="n">
-        <v>14470</v>
+        <v>24792</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>112.32</v>
+        <v>137.49</v>
       </c>
       <c r="B383" t="n">
-        <v>25561</v>
+        <v>18810</v>
       </c>
       <c r="C383" t="n">
-        <v>115.76</v>
+        <v>119.55</v>
       </c>
       <c r="D383" t="n">
-        <v>26655</v>
+        <v>11539</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>114.7</v>
+        <v>137.71</v>
       </c>
       <c r="B384" t="n">
-        <v>23321</v>
+        <v>19484</v>
       </c>
       <c r="C384" t="n">
-        <v>114.55</v>
+        <v>153.29</v>
       </c>
       <c r="D384" t="n">
-        <v>28653</v>
+        <v>17896</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>31.4</v>
+        <v>137.77</v>
       </c>
       <c r="B385" t="n">
-        <v>21583</v>
+        <v>21374</v>
       </c>
       <c r="C385" t="n">
-        <v>31.49</v>
+        <v>139.85</v>
       </c>
       <c r="D385" t="n">
-        <v>10076</v>
+        <v>23662</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>99.37</v>
+        <v>138</v>
       </c>
       <c r="B386" t="n">
-        <v>43068</v>
+        <v>17649</v>
       </c>
       <c r="C386" t="n">
-        <v>100.11</v>
+        <v>149.91</v>
       </c>
       <c r="D386" t="n">
-        <v>24169</v>
+        <v>18325</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>103.08</v>
+        <v>138.78</v>
       </c>
       <c r="B387" t="n">
-        <v>48914</v>
+        <v>19151</v>
       </c>
       <c r="C387" t="n">
-        <v>100.59</v>
+        <v>146.9</v>
       </c>
       <c r="D387" t="n">
-        <v>19229</v>
+        <v>26600</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>105.61</v>
+        <v>138.91</v>
       </c>
       <c r="B388" t="n">
-        <v>42049</v>
+        <v>18225</v>
       </c>
       <c r="C388" t="n">
-        <v>101.71</v>
+        <v>142.99</v>
       </c>
       <c r="D388" t="n">
-        <v>22517</v>
+        <v>20835</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>144.62</v>
+        <v>139.23</v>
       </c>
       <c r="B389" t="n">
-        <v>23726</v>
+        <v>17780</v>
       </c>
       <c r="C389" t="n">
-        <v>139.21</v>
+        <v>104.26</v>
       </c>
       <c r="D389" t="n">
-        <v>12071</v>
+        <v>22444</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>92.87</v>
+        <v>140.07</v>
       </c>
       <c r="B390" t="n">
-        <v>29054</v>
+        <v>23185</v>
       </c>
       <c r="C390" t="n">
-        <v>89.22</v>
+        <v>111.3</v>
       </c>
       <c r="D390" t="n">
-        <v>22590</v>
+        <v>15089</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>81.47</v>
+        <v>140.08</v>
       </c>
       <c r="B391" t="n">
-        <v>21461</v>
+        <v>21425</v>
       </c>
       <c r="C391" t="n">
-        <v>80.28</v>
+        <v>147.27</v>
       </c>
       <c r="D391" t="n">
-        <v>28231</v>
+        <v>27266</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>107.93</v>
+        <v>140.46</v>
       </c>
       <c r="B392" t="n">
-        <v>37312</v>
+        <v>20336</v>
       </c>
       <c r="C392" t="n">
-        <v>112.83</v>
+        <v>131.19</v>
       </c>
       <c r="D392" t="n">
-        <v>27382</v>
+        <v>29637</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>102.17</v>
+        <v>140.79</v>
       </c>
       <c r="B393" t="n">
-        <v>46810</v>
+        <v>20178</v>
       </c>
       <c r="C393" t="n">
-        <v>102.06</v>
+        <v>154.97</v>
       </c>
       <c r="D393" t="n">
-        <v>14270</v>
+        <v>29285</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>93.14</v>
+        <v>141.2</v>
       </c>
       <c r="B394" t="n">
-        <v>30209</v>
+        <v>18403</v>
       </c>
       <c r="C394" t="n">
-        <v>95.14</v>
+        <v>157.73</v>
       </c>
       <c r="D394" t="n">
-        <v>19768</v>
+        <v>17890</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>107.56</v>
+        <v>141.95</v>
       </c>
       <c r="B395" t="n">
-        <v>41661</v>
+        <v>20694</v>
       </c>
       <c r="C395" t="n">
-        <v>108.97</v>
+        <v>129.42</v>
       </c>
       <c r="D395" t="n">
-        <v>24422</v>
+        <v>29149</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>90.59</v>
+        <v>142.56</v>
       </c>
       <c r="B396" t="n">
-        <v>24898</v>
+        <v>19279</v>
       </c>
       <c r="C396" t="n">
-        <v>87.47</v>
+        <v>159.19</v>
       </c>
       <c r="D396" t="n">
-        <v>15165</v>
+        <v>24645</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>30.24</v>
+        <v>142.72</v>
       </c>
       <c r="B397" t="n">
-        <v>24273</v>
+        <v>20827</v>
       </c>
       <c r="C397" t="n">
-        <v>29.83</v>
+        <v>149.22</v>
       </c>
       <c r="D397" t="n">
-        <v>17572</v>
+        <v>21286</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>105.83</v>
+        <v>143.07</v>
       </c>
       <c r="B398" t="n">
-        <v>44279</v>
+        <v>18811</v>
       </c>
       <c r="C398" t="n">
-        <v>105.3</v>
+        <v>169.85</v>
       </c>
       <c r="D398" t="n">
-        <v>19989</v>
+        <v>22518</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>97.97</v>
+        <v>143.13</v>
       </c>
       <c r="B399" t="n">
-        <v>42873</v>
+        <v>21617</v>
       </c>
       <c r="C399" t="n">
-        <v>98</v>
+        <v>115.15</v>
       </c>
       <c r="D399" t="n">
-        <v>13770</v>
+        <v>13248</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>114.64</v>
+        <v>143.51</v>
       </c>
       <c r="B400" t="n">
-        <v>25132</v>
+        <v>18566</v>
       </c>
       <c r="C400" t="n">
-        <v>115.06</v>
+        <v>147.9</v>
       </c>
       <c r="D400" t="n">
-        <v>25609</v>
+        <v>26976</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>176.41</v>
+        <v>143.59</v>
       </c>
       <c r="B401" t="n">
-        <v>23963</v>
+        <v>19555</v>
       </c>
       <c r="C401" t="n">
-        <v>170.65</v>
+        <v>132.55</v>
       </c>
       <c r="D401" t="n">
-        <v>13541</v>
+        <v>14460</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>101.64</v>
+        <v>143.77</v>
       </c>
       <c r="B402" t="n">
-        <v>48675</v>
+        <v>21190</v>
       </c>
       <c r="C402" t="n">
-        <v>99.73</v>
+        <v>127.84</v>
       </c>
       <c r="D402" t="n">
-        <v>13775</v>
+        <v>21327</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>96.97</v>
+        <v>144</v>
       </c>
       <c r="B403" t="n">
-        <v>39240</v>
+        <v>19694</v>
       </c>
       <c r="C403" t="n">
-        <v>97.14</v>
+        <v>164.79</v>
       </c>
       <c r="D403" t="n">
-        <v>18834</v>
+        <v>15452</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>111.03</v>
+        <v>144.22</v>
       </c>
       <c r="B404" t="n">
-        <v>31199</v>
+        <v>21228</v>
       </c>
       <c r="C404" t="n">
-        <v>113.02</v>
+        <v>127.57</v>
       </c>
       <c r="D404" t="n">
-        <v>24709</v>
+        <v>18228</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>101.94</v>
+        <v>144.99</v>
       </c>
       <c r="B405" t="n">
-        <v>43482</v>
+        <v>22000</v>
       </c>
       <c r="C405" t="n">
-        <v>99.91</v>
+        <v>153.67</v>
       </c>
       <c r="D405" t="n">
-        <v>26469</v>
+        <v>26601</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>47.65</v>
+        <v>145.31</v>
       </c>
       <c r="B406" t="n">
-        <v>23388</v>
+        <v>22156</v>
       </c>
       <c r="C406" t="n">
-        <v>46.67</v>
+        <v>141.79</v>
       </c>
       <c r="D406" t="n">
-        <v>14757</v>
+        <v>10298</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>94.02</v>
+        <v>146.07</v>
       </c>
       <c r="B407" t="n">
-        <v>31537</v>
+        <v>21323</v>
       </c>
       <c r="C407" t="n">
-        <v>96.87</v>
+        <v>161.2</v>
       </c>
       <c r="D407" t="n">
-        <v>29076</v>
+        <v>11757</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>102.84</v>
+        <v>146.24</v>
       </c>
       <c r="B408" t="n">
-        <v>48762</v>
+        <v>25946</v>
       </c>
       <c r="C408" t="n">
-        <v>101.14</v>
+        <v>151.54</v>
       </c>
       <c r="D408" t="n">
-        <v>12514</v>
+        <v>28589</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>74.91</v>
+        <v>146.4</v>
       </c>
       <c r="B409" t="n">
-        <v>24124</v>
+        <v>19176</v>
       </c>
       <c r="C409" t="n">
-        <v>72.65000000000001</v>
+        <v>127.22</v>
       </c>
       <c r="D409" t="n">
-        <v>19477</v>
+        <v>21682</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>111.7</v>
+        <v>146.48</v>
       </c>
       <c r="B410" t="n">
-        <v>28165</v>
+        <v>24552</v>
       </c>
       <c r="C410" t="n">
-        <v>108.88</v>
+        <v>158.22</v>
       </c>
       <c r="D410" t="n">
-        <v>10721</v>
+        <v>22245</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>110.86</v>
+        <v>147.54</v>
       </c>
       <c r="B411" t="n">
-        <v>29993</v>
+        <v>22886</v>
       </c>
       <c r="C411" t="n">
-        <v>112.16</v>
+        <v>144.35</v>
       </c>
       <c r="D411" t="n">
-        <v>22405</v>
+        <v>21055</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>111.03</v>
+        <v>147.55</v>
       </c>
       <c r="B412" t="n">
-        <v>29998</v>
+        <v>23945</v>
       </c>
       <c r="C412" t="n">
-        <v>107.89</v>
+        <v>161.38</v>
       </c>
       <c r="D412" t="n">
-        <v>15858</v>
+        <v>23189</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>96.81</v>
+        <v>147.59</v>
       </c>
       <c r="B413" t="n">
-        <v>39710</v>
+        <v>23153</v>
       </c>
       <c r="C413" t="n">
-        <v>93.04000000000001</v>
+        <v>122.92</v>
       </c>
       <c r="D413" t="n">
-        <v>17260</v>
+        <v>22950</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>81.36</v>
+        <v>148.18</v>
       </c>
       <c r="B414" t="n">
-        <v>25925</v>
+        <v>20542</v>
       </c>
       <c r="C414" t="n">
-        <v>80.40000000000001</v>
+        <v>134.23</v>
       </c>
       <c r="D414" t="n">
-        <v>29731</v>
+        <v>17453</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>158.94</v>
+        <v>148.79</v>
       </c>
       <c r="B415" t="n">
-        <v>21795</v>
+        <v>23035</v>
       </c>
       <c r="C415" t="n">
-        <v>160.61</v>
+        <v>180</v>
       </c>
       <c r="D415" t="n">
-        <v>15714</v>
+        <v>23553</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>100.73</v>
+        <v>149.55</v>
       </c>
       <c r="B416" t="n">
-        <v>44627</v>
+        <v>22712</v>
       </c>
       <c r="C416" t="n">
-        <v>104.06</v>
+        <v>137.88</v>
       </c>
       <c r="D416" t="n">
-        <v>17536</v>
+        <v>26745</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>108.31</v>
+        <v>149.83</v>
       </c>
       <c r="B417" t="n">
-        <v>40602</v>
+        <v>20425</v>
       </c>
       <c r="C417" t="n">
-        <v>110.19</v>
+        <v>171.18</v>
       </c>
       <c r="D417" t="n">
-        <v>18169</v>
+        <v>27355</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>92.37</v>
+        <v>149.85</v>
       </c>
       <c r="B418" t="n">
-        <v>24818</v>
+        <v>22807</v>
       </c>
       <c r="C418" t="n">
-        <v>94.63</v>
+        <v>127.68</v>
       </c>
       <c r="D418" t="n">
-        <v>12154</v>
+        <v>21745</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>90.63</v>
+        <v>150.02</v>
       </c>
       <c r="B419" t="n">
-        <v>23589</v>
+        <v>25154</v>
       </c>
       <c r="C419" t="n">
-        <v>93.61</v>
+        <v>165.06</v>
       </c>
       <c r="D419" t="n">
-        <v>16297</v>
+        <v>16303</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>114.62</v>
+        <v>150.71</v>
       </c>
       <c r="B420" t="n">
-        <v>21347</v>
+        <v>24345</v>
       </c>
       <c r="C420" t="n">
-        <v>118.14</v>
+        <v>155.91</v>
       </c>
       <c r="D420" t="n">
-        <v>14056</v>
+        <v>16257</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>98.91</v>
+        <v>151.23</v>
       </c>
       <c r="B421" t="n">
-        <v>40991</v>
+        <v>24501</v>
       </c>
       <c r="C421" t="n">
-        <v>97.39</v>
+        <v>155.93</v>
       </c>
       <c r="D421" t="n">
-        <v>25087</v>
+        <v>17579</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>102.85</v>
+        <v>151.82</v>
       </c>
       <c r="B422" t="n">
-        <v>48417</v>
+        <v>24584</v>
       </c>
       <c r="C422" t="n">
-        <v>100.75</v>
+        <v>135.56</v>
       </c>
       <c r="D422" t="n">
-        <v>26239</v>
+        <v>13823</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>164.15</v>
+        <v>151.95</v>
       </c>
       <c r="B423" t="n">
-        <v>22584</v>
+        <v>23100</v>
       </c>
       <c r="C423" t="n">
-        <v>157.49</v>
+        <v>130.54</v>
       </c>
       <c r="D423" t="n">
-        <v>24591</v>
+        <v>13835</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>99.37</v>
+        <v>152.53</v>
       </c>
       <c r="B424" t="n">
-        <v>43542</v>
+        <v>24898</v>
       </c>
       <c r="C424" t="n">
-        <v>101.29</v>
+        <v>127.46</v>
       </c>
       <c r="D424" t="n">
-        <v>15963</v>
+        <v>22319</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>111.59</v>
+        <v>153.29</v>
       </c>
       <c r="B425" t="n">
-        <v>25812</v>
+        <v>28322</v>
       </c>
       <c r="C425" t="n">
-        <v>111.03</v>
+        <v>141.73</v>
       </c>
       <c r="D425" t="n">
-        <v>22054</v>
+        <v>20411</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>115.11</v>
+        <v>153.36</v>
       </c>
       <c r="B426" t="n">
-        <v>22796</v>
+        <v>25838</v>
       </c>
       <c r="C426" t="n">
-        <v>111.72</v>
+        <v>144.38</v>
       </c>
       <c r="D426" t="n">
-        <v>12655</v>
+        <v>15199</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>104.65</v>
+        <v>154.68</v>
       </c>
       <c r="B427" t="n">
-        <v>46300</v>
+        <v>29217</v>
       </c>
       <c r="C427" t="n">
-        <v>101.04</v>
+        <v>174.6</v>
       </c>
       <c r="D427" t="n">
-        <v>12354</v>
+        <v>27344</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>96.23</v>
+        <v>154.76</v>
       </c>
       <c r="B428" t="n">
-        <v>36504</v>
+        <v>28568</v>
       </c>
       <c r="C428" t="n">
-        <v>97.81999999999999</v>
+        <v>174.32</v>
       </c>
       <c r="D428" t="n">
-        <v>15845</v>
+        <v>14430</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>111.91</v>
+        <v>154.82</v>
       </c>
       <c r="B429" t="n">
-        <v>27280</v>
+        <v>29636</v>
       </c>
       <c r="C429" t="n">
-        <v>110.34</v>
+        <v>165.86</v>
       </c>
       <c r="D429" t="n">
-        <v>25100</v>
+        <v>14330</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>114.96</v>
+        <v>155.29</v>
       </c>
       <c r="B430" t="n">
-        <v>24354</v>
+        <v>29461</v>
       </c>
       <c r="C430" t="n">
-        <v>114.58</v>
+        <v>125.98</v>
       </c>
       <c r="D430" t="n">
-        <v>13207</v>
+        <v>20978</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>99.69</v>
+        <v>155.46</v>
       </c>
       <c r="B431" t="n">
-        <v>43858</v>
+        <v>29889</v>
       </c>
       <c r="C431" t="n">
-        <v>98.81</v>
+        <v>177.85</v>
       </c>
       <c r="D431" t="n">
-        <v>17161</v>
+        <v>21900</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>103.12</v>
+        <v>156.42</v>
       </c>
       <c r="B432" t="n">
-        <v>48272</v>
+        <v>29714</v>
       </c>
       <c r="C432" t="n">
-        <v>100.49</v>
+        <v>166.2</v>
       </c>
       <c r="D432" t="n">
-        <v>27683</v>
+        <v>16622</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>97.2</v>
+        <v>156.82</v>
       </c>
       <c r="B433" t="n">
-        <v>38023</v>
+        <v>28578</v>
       </c>
       <c r="C433" t="n">
-        <v>93.33</v>
+        <v>124.58</v>
       </c>
       <c r="D433" t="n">
-        <v>25807</v>
+        <v>18171</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>32.89</v>
+        <v>157.05</v>
       </c>
       <c r="B434" t="n">
-        <v>24542</v>
+        <v>30031</v>
       </c>
       <c r="C434" t="n">
-        <v>33.83</v>
+        <v>180</v>
       </c>
       <c r="D434" t="n">
-        <v>17336</v>
+        <v>27735</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>97.33</v>
+        <v>157.15</v>
       </c>
       <c r="B435" t="n">
-        <v>40165</v>
+        <v>29453</v>
       </c>
       <c r="C435" t="n">
-        <v>97.14</v>
+        <v>179.13</v>
       </c>
       <c r="D435" t="n">
-        <v>10799</v>
+        <v>20091</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>95.70999999999999</v>
+        <v>158.02</v>
       </c>
       <c r="B436" t="n">
-        <v>36448</v>
+        <v>29740</v>
       </c>
       <c r="C436" t="n">
-        <v>94.97</v>
+        <v>149.55</v>
       </c>
       <c r="D436" t="n">
-        <v>14822</v>
+        <v>24992</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>109.56</v>
+        <v>158.04</v>
       </c>
       <c r="B437" t="n">
-        <v>34254</v>
+        <v>27354</v>
       </c>
       <c r="C437" t="n">
-        <v>110.29</v>
+        <v>137.28</v>
       </c>
       <c r="D437" t="n">
-        <v>11682</v>
+        <v>19916</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>93.84999999999999</v>
+        <v>158.07</v>
       </c>
       <c r="B438" t="n">
-        <v>29758</v>
+        <v>30254</v>
       </c>
       <c r="C438" t="n">
-        <v>90.65000000000001</v>
+        <v>124.22</v>
       </c>
       <c r="D438" t="n">
-        <v>19943</v>
+        <v>24616</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>30.96</v>
+        <v>158.37</v>
       </c>
       <c r="B439" t="n">
-        <v>26225</v>
+        <v>30134</v>
       </c>
       <c r="C439" t="n">
-        <v>30.35</v>
+        <v>160.66</v>
       </c>
       <c r="D439" t="n">
-        <v>20737</v>
+        <v>18297</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>8.279999999999999</v>
+        <v>158.37</v>
       </c>
       <c r="B440" t="n">
-        <v>22975</v>
+        <v>29870</v>
       </c>
       <c r="C440" t="n">
-        <v>7.76</v>
+        <v>180</v>
       </c>
       <c r="D440" t="n">
-        <v>27633</v>
+        <v>23591</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>114.94</v>
+        <v>158.54</v>
       </c>
       <c r="B441" t="n">
-        <v>21092</v>
+        <v>29503</v>
       </c>
       <c r="C441" t="n">
-        <v>112.19</v>
+        <v>179.54</v>
       </c>
       <c r="D441" t="n">
-        <v>28508</v>
+        <v>11803</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>92.17</v>
+        <v>159.37</v>
       </c>
       <c r="B442" t="n">
-        <v>26279</v>
+        <v>31755</v>
       </c>
       <c r="C442" t="n">
-        <v>91.56</v>
+        <v>140.48</v>
       </c>
       <c r="D442" t="n">
-        <v>13040</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>97.01000000000001</v>
+        <v>159.64</v>
       </c>
       <c r="B443" t="n">
-        <v>39543</v>
+        <v>32463</v>
       </c>
       <c r="C443" t="n">
-        <v>95.15000000000001</v>
+        <v>174.02</v>
       </c>
       <c r="D443" t="n">
-        <v>24114</v>
+        <v>14908</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>106.72</v>
+        <v>160.57</v>
       </c>
       <c r="B444" t="n">
-        <v>42891</v>
+        <v>29580</v>
       </c>
       <c r="C444" t="n">
-        <v>108.62</v>
+        <v>167.99</v>
       </c>
       <c r="D444" t="n">
-        <v>18869</v>
+        <v>12918</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>108.77</v>
+        <v>161.9</v>
       </c>
       <c r="B445" t="n">
-        <v>37084</v>
+        <v>27047</v>
       </c>
       <c r="C445" t="n">
-        <v>112.3</v>
+        <v>130.13</v>
       </c>
       <c r="D445" t="n">
-        <v>13825</v>
+        <v>27475</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>103.23</v>
+        <v>162.41</v>
       </c>
       <c r="B446" t="n">
-        <v>45079</v>
+        <v>30395</v>
       </c>
       <c r="C446" t="n">
-        <v>103.97</v>
+        <v>180</v>
       </c>
       <c r="D446" t="n">
-        <v>17118</v>
+        <v>20976</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>98.73</v>
+        <v>162.44</v>
       </c>
       <c r="B447" t="n">
-        <v>42114</v>
+        <v>31606</v>
       </c>
       <c r="C447" t="n">
-        <v>101.73</v>
+        <v>176.11</v>
       </c>
       <c r="D447" t="n">
-        <v>24585</v>
+        <v>25669</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>167.83</v>
+        <v>162.56</v>
       </c>
       <c r="B448" t="n">
-        <v>23810</v>
+        <v>31130</v>
       </c>
       <c r="C448" t="n">
-        <v>164.08</v>
+        <v>127.28</v>
       </c>
       <c r="D448" t="n">
-        <v>16364</v>
+        <v>24451</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>100.75</v>
+        <v>162.86</v>
       </c>
       <c r="B449" t="n">
-        <v>43304</v>
+        <v>30082</v>
       </c>
       <c r="C449" t="n">
-        <v>99.76000000000001</v>
+        <v>163.1</v>
       </c>
       <c r="D449" t="n">
-        <v>27959</v>
+        <v>17320</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>82.28</v>
+        <v>162.87</v>
       </c>
       <c r="B450" t="n">
-        <v>23839</v>
+        <v>30579</v>
       </c>
       <c r="C450" t="n">
-        <v>84.18000000000001</v>
+        <v>179.05</v>
       </c>
       <c r="D450" t="n">
-        <v>10026</v>
+        <v>27614</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>94.06</v>
+        <v>163.41</v>
       </c>
       <c r="B451" t="n">
-        <v>32305</v>
+        <v>29970</v>
       </c>
       <c r="C451" t="n">
-        <v>97.91</v>
+        <v>170.23</v>
       </c>
       <c r="D451" t="n">
-        <v>18422</v>
+        <v>12763</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>72.34</v>
+        <v>163.8</v>
       </c>
       <c r="B452" t="n">
-        <v>25991</v>
+        <v>28648</v>
       </c>
       <c r="C452" t="n">
-        <v>70.2</v>
+        <v>162.64</v>
       </c>
       <c r="D452" t="n">
-        <v>22158</v>
+        <v>17885</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>95.84999999999999</v>
+        <v>163.8</v>
       </c>
       <c r="B453" t="n">
-        <v>33775</v>
+        <v>26629</v>
       </c>
       <c r="C453" t="n">
-        <v>95.23</v>
+        <v>166.48</v>
       </c>
       <c r="D453" t="n">
-        <v>21939</v>
+        <v>28331</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>131.84</v>
+        <v>164.14</v>
       </c>
       <c r="B454" t="n">
-        <v>23363</v>
+        <v>29835</v>
       </c>
       <c r="C454" t="n">
-        <v>131.64</v>
+        <v>174.94</v>
       </c>
       <c r="D454" t="n">
-        <v>19500</v>
+        <v>19915</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>31.6</v>
+        <v>164.71</v>
       </c>
       <c r="B455" t="n">
-        <v>24483</v>
+        <v>27882</v>
       </c>
       <c r="C455" t="n">
-        <v>32.72</v>
+        <v>180</v>
       </c>
       <c r="D455" t="n">
-        <v>10966</v>
+        <v>29455</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>153.8</v>
+        <v>164.74</v>
       </c>
       <c r="B456" t="n">
-        <v>24602</v>
+        <v>28229</v>
       </c>
       <c r="C456" t="n">
-        <v>152.83</v>
+        <v>180</v>
       </c>
       <c r="D456" t="n">
-        <v>13885</v>
+        <v>18251</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>74.08</v>
+        <v>164.78</v>
       </c>
       <c r="B457" t="n">
-        <v>22030</v>
+        <v>27891</v>
       </c>
       <c r="C457" t="n">
-        <v>75.70999999999999</v>
+        <v>169.15</v>
       </c>
       <c r="D457" t="n">
-        <v>11319</v>
+        <v>10912</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>113.94</v>
+        <v>165.04</v>
       </c>
       <c r="B458" t="n">
-        <v>24284</v>
+        <v>28886</v>
       </c>
       <c r="C458" t="n">
-        <v>110.68</v>
+        <v>130.66</v>
       </c>
       <c r="D458" t="n">
-        <v>14855</v>
+        <v>17487</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>91.76000000000001</v>
+        <v>165.75</v>
       </c>
       <c r="B459" t="n">
-        <v>25775</v>
+        <v>29703</v>
       </c>
       <c r="C459" t="n">
-        <v>95.67</v>
+        <v>180</v>
       </c>
       <c r="D459" t="n">
-        <v>16468</v>
+        <v>28612</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>97.92</v>
+        <v>165.8</v>
       </c>
       <c r="B460" t="n">
-        <v>43274</v>
+        <v>26688</v>
       </c>
       <c r="C460" t="n">
-        <v>97.12</v>
+        <v>161.25</v>
       </c>
       <c r="D460" t="n">
-        <v>21062</v>
+        <v>26440</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>95.54000000000001</v>
+        <v>166.14</v>
       </c>
       <c r="B461" t="n">
-        <v>35967</v>
+        <v>26565</v>
       </c>
       <c r="C461" t="n">
-        <v>98.09999999999999</v>
+        <v>145.64</v>
       </c>
       <c r="D461" t="n">
-        <v>12989</v>
+        <v>20950</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>110.3</v>
+        <v>166.82</v>
       </c>
       <c r="B462" t="n">
-        <v>30713</v>
+        <v>25561</v>
       </c>
       <c r="C462" t="n">
-        <v>109.3</v>
+        <v>165.52</v>
       </c>
       <c r="D462" t="n">
-        <v>25012</v>
+        <v>11562</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>154.79</v>
+        <v>166.85</v>
       </c>
       <c r="B463" t="n">
-        <v>25018</v>
+        <v>26370</v>
       </c>
       <c r="C463" t="n">
-        <v>152.71</v>
+        <v>172.66</v>
       </c>
       <c r="D463" t="n">
-        <v>27091</v>
+        <v>12115</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>111.68</v>
+        <v>168.02</v>
       </c>
       <c r="B464" t="n">
-        <v>28741</v>
+        <v>25202</v>
       </c>
       <c r="C464" t="n">
-        <v>114.77</v>
+        <v>166.91</v>
       </c>
       <c r="D464" t="n">
-        <v>21053</v>
+        <v>23010</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>107.98</v>
+        <v>168.23</v>
       </c>
       <c r="B465" t="n">
-        <v>38407</v>
+        <v>26344</v>
       </c>
       <c r="C465" t="n">
-        <v>107.93</v>
+        <v>133.73</v>
       </c>
       <c r="D465" t="n">
-        <v>28097</v>
+        <v>23820</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>110.52</v>
+        <v>168.32</v>
       </c>
       <c r="B466" t="n">
-        <v>31711</v>
+        <v>27299</v>
       </c>
       <c r="C466" t="n">
-        <v>108.8</v>
+        <v>169.58</v>
       </c>
       <c r="D466" t="n">
-        <v>10182</v>
+        <v>29784</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>99.45999999999999</v>
+        <v>168.61</v>
       </c>
       <c r="B467" t="n">
-        <v>43194</v>
+        <v>24823</v>
       </c>
       <c r="C467" t="n">
-        <v>95.77</v>
+        <v>173.6</v>
       </c>
       <c r="D467" t="n">
-        <v>14962</v>
+        <v>12682</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>102.88</v>
+        <v>169.1</v>
       </c>
       <c r="B468" t="n">
-        <v>45774</v>
+        <v>25293</v>
       </c>
       <c r="C468" t="n">
-        <v>103.71</v>
+        <v>139.3</v>
       </c>
       <c r="D468" t="n">
-        <v>21081</v>
+        <v>14183</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>90.5</v>
+        <v>169.44</v>
       </c>
       <c r="B469" t="n">
-        <v>24602</v>
+        <v>23578</v>
       </c>
       <c r="C469" t="n">
-        <v>91.06999999999999</v>
+        <v>180</v>
       </c>
       <c r="D469" t="n">
-        <v>18922</v>
+        <v>29878</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>109.92</v>
+        <v>170.73</v>
       </c>
       <c r="B470" t="n">
-        <v>30472</v>
+        <v>21095</v>
       </c>
       <c r="C470" t="n">
-        <v>114.25</v>
+        <v>177.91</v>
       </c>
       <c r="D470" t="n">
-        <v>12537</v>
+        <v>10981</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>99.17</v>
+        <v>171.07</v>
       </c>
       <c r="B471" t="n">
-        <v>43958</v>
+        <v>22683</v>
       </c>
       <c r="C471" t="n">
-        <v>95.56</v>
+        <v>150.37</v>
       </c>
       <c r="D471" t="n">
-        <v>26240</v>
+        <v>21427</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>102.46</v>
+        <v>171.44</v>
       </c>
       <c r="B472" t="n">
-        <v>46830</v>
+        <v>23687</v>
       </c>
       <c r="C472" t="n">
-        <v>105.23</v>
+        <v>180</v>
       </c>
       <c r="D472" t="n">
-        <v>10609</v>
+        <v>29386</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>69.14</v>
+        <v>171.73</v>
       </c>
       <c r="B473" t="n">
-        <v>24378</v>
+        <v>23338</v>
       </c>
       <c r="C473" t="n">
-        <v>69.48</v>
+        <v>152.49</v>
       </c>
       <c r="D473" t="n">
-        <v>22830</v>
+        <v>13187</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>97.3</v>
+        <v>171.81</v>
       </c>
       <c r="B474" t="n">
-        <v>39287</v>
+        <v>19787</v>
       </c>
       <c r="C474" t="n">
-        <v>95.42</v>
+        <v>180</v>
       </c>
       <c r="D474" t="n">
-        <v>29050</v>
+        <v>27944</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>141.96</v>
+        <v>172.2</v>
       </c>
       <c r="B475" t="n">
-        <v>24049</v>
+        <v>18013</v>
       </c>
       <c r="C475" t="n">
-        <v>142.16</v>
+        <v>180</v>
       </c>
       <c r="D475" t="n">
-        <v>11704</v>
+        <v>27883</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>32.7</v>
+        <v>172.2</v>
       </c>
       <c r="B476" t="n">
-        <v>22417</v>
+        <v>23826</v>
       </c>
       <c r="C476" t="n">
-        <v>32.61</v>
+        <v>180</v>
       </c>
       <c r="D476" t="n">
-        <v>27347</v>
+        <v>25266</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>96.88</v>
+        <v>172.44</v>
       </c>
       <c r="B477" t="n">
-        <v>38513</v>
+        <v>21053</v>
       </c>
       <c r="C477" t="n">
-        <v>99.84999999999999</v>
+        <v>178.43</v>
       </c>
       <c r="D477" t="n">
-        <v>14895</v>
+        <v>25524</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>107.1</v>
+        <v>172.72</v>
       </c>
       <c r="B478" t="n">
-        <v>43139</v>
+        <v>21651</v>
       </c>
       <c r="C478" t="n">
-        <v>105.31</v>
+        <v>180</v>
       </c>
       <c r="D478" t="n">
-        <v>10582</v>
+        <v>13118</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>110.4</v>
+        <v>172.73</v>
       </c>
       <c r="B479" t="n">
-        <v>31016</v>
+        <v>22300</v>
       </c>
       <c r="C479" t="n">
-        <v>110.08</v>
+        <v>180</v>
       </c>
       <c r="D479" t="n">
-        <v>20402</v>
+        <v>18932</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>103.77</v>
+        <v>172.75</v>
       </c>
       <c r="B480" t="n">
-        <v>44153</v>
+        <v>20292</v>
       </c>
       <c r="C480" t="n">
-        <v>107.88</v>
+        <v>180</v>
       </c>
       <c r="D480" t="n">
-        <v>17236</v>
+        <v>11335</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>105.59</v>
+        <v>172.94</v>
       </c>
       <c r="B481" t="n">
-        <v>47146</v>
+        <v>20768</v>
       </c>
       <c r="C481" t="n">
-        <v>102.17</v>
+        <v>151.16</v>
       </c>
       <c r="D481" t="n">
-        <v>20120</v>
+        <v>12451</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>35.86</v>
+        <v>174.28</v>
       </c>
       <c r="B482" t="n">
-        <v>24961</v>
+        <v>22185</v>
       </c>
       <c r="C482" t="n">
-        <v>36.56</v>
+        <v>180</v>
       </c>
       <c r="D482" t="n">
-        <v>26866</v>
+        <v>16950</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>95.73999999999999</v>
+        <v>174.6</v>
       </c>
       <c r="B483" t="n">
-        <v>38400</v>
+        <v>21274</v>
       </c>
       <c r="C483" t="n">
-        <v>99.33</v>
+        <v>153.74</v>
       </c>
       <c r="D483" t="n">
-        <v>22221</v>
+        <v>23129</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>96.34</v>
+        <v>175.41</v>
       </c>
       <c r="B484" t="n">
-        <v>36485</v>
+        <v>17337</v>
       </c>
       <c r="C484" t="n">
-        <v>98.12</v>
+        <v>157.15</v>
       </c>
       <c r="D484" t="n">
-        <v>15946</v>
+        <v>21015</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>98.54000000000001</v>
+        <v>175.44</v>
       </c>
       <c r="B485" t="n">
-        <v>39719</v>
+        <v>20039</v>
       </c>
       <c r="C485" t="n">
-        <v>97.06</v>
+        <v>180</v>
       </c>
       <c r="D485" t="n">
-        <v>20690</v>
+        <v>18750</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>112.71</v>
+        <v>175.74</v>
       </c>
       <c r="B486" t="n">
-        <v>24265</v>
+        <v>22399</v>
       </c>
       <c r="C486" t="n">
-        <v>109.9</v>
+        <v>180</v>
       </c>
       <c r="D486" t="n">
-        <v>22106</v>
+        <v>14552</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>97.48</v>
+        <v>175.77</v>
       </c>
       <c r="B487" t="n">
-        <v>39188</v>
+        <v>18634</v>
       </c>
       <c r="C487" t="n">
-        <v>99.16</v>
+        <v>170.54</v>
       </c>
       <c r="D487" t="n">
-        <v>17209</v>
+        <v>10994</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>114.95</v>
+        <v>175.86</v>
       </c>
       <c r="B488" t="n">
-        <v>22928</v>
+        <v>17779</v>
       </c>
       <c r="C488" t="n">
-        <v>115.59</v>
+        <v>180</v>
       </c>
       <c r="D488" t="n">
-        <v>19604</v>
+        <v>18807</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>114.11</v>
+        <v>175.89</v>
       </c>
       <c r="B489" t="n">
-        <v>24246</v>
+        <v>20504</v>
       </c>
       <c r="C489" t="n">
-        <v>113.53</v>
+        <v>173.37</v>
       </c>
       <c r="D489" t="n">
-        <v>22232</v>
+        <v>27730</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>100.98</v>
+        <v>176.39</v>
       </c>
       <c r="B490" t="n">
-        <v>44366</v>
+        <v>18408</v>
       </c>
       <c r="C490" t="n">
-        <v>100.36</v>
+        <v>155.37</v>
       </c>
       <c r="D490" t="n">
-        <v>26702</v>
+        <v>16452</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>104.06</v>
+        <v>176.45</v>
       </c>
       <c r="B491" t="n">
-        <v>47220</v>
+        <v>20812</v>
       </c>
       <c r="C491" t="n">
-        <v>102.1</v>
+        <v>180</v>
       </c>
       <c r="D491" t="n">
-        <v>20533</v>
+        <v>17594</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>105.69</v>
+        <v>176.73</v>
       </c>
       <c r="B492" t="n">
-        <v>42613</v>
+        <v>17955</v>
       </c>
       <c r="C492" t="n">
-        <v>107.15</v>
+        <v>180</v>
       </c>
       <c r="D492" t="n">
-        <v>15341</v>
+        <v>26563</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>101.73</v>
+        <v>176.97</v>
       </c>
       <c r="B493" t="n">
-        <v>43703</v>
+        <v>20783</v>
       </c>
       <c r="C493" t="n">
-        <v>103.21</v>
+        <v>179.8</v>
       </c>
       <c r="D493" t="n">
-        <v>15073</v>
+        <v>27175</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>95.3</v>
+        <v>177.02</v>
       </c>
       <c r="B494" t="n">
-        <v>36801</v>
+        <v>19593</v>
       </c>
       <c r="C494" t="n">
-        <v>97.09</v>
+        <v>180</v>
       </c>
       <c r="D494" t="n">
-        <v>15287</v>
+        <v>11933</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>137.43</v>
+        <v>177.71</v>
       </c>
       <c r="B495" t="n">
-        <v>21888</v>
+        <v>19145</v>
       </c>
       <c r="C495" t="n">
-        <v>135.35</v>
+        <v>180</v>
       </c>
       <c r="D495" t="n">
-        <v>16309</v>
+        <v>21837</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>90.41</v>
+        <v>177.72</v>
       </c>
       <c r="B496" t="n">
-        <v>24444</v>
+        <v>19013</v>
       </c>
       <c r="C496" t="n">
-        <v>87.64</v>
+        <v>165.64</v>
       </c>
       <c r="D496" t="n">
-        <v>26275</v>
+        <v>22928</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>105.4</v>
+        <v>179.07</v>
       </c>
       <c r="B497" t="n">
-        <v>46515</v>
+        <v>19851</v>
       </c>
       <c r="C497" t="n">
-        <v>104.58</v>
+        <v>175.33</v>
       </c>
       <c r="D497" t="n">
-        <v>23346</v>
+        <v>18593</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>91.03</v>
+        <v>179.3</v>
       </c>
       <c r="B498" t="n">
-        <v>25405</v>
+        <v>19361</v>
       </c>
       <c r="C498" t="n">
-        <v>89.62</v>
+        <v>180</v>
       </c>
       <c r="D498" t="n">
-        <v>12546</v>
+        <v>22254</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>105.97</v>
+        <v>179.51</v>
       </c>
       <c r="B499" t="n">
-        <v>44178</v>
+        <v>17241</v>
       </c>
       <c r="C499" t="n">
-        <v>103.85</v>
+        <v>180</v>
       </c>
       <c r="D499" t="n">
-        <v>22130</v>
+        <v>25443</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>45.64</v>
+        <v>179.61</v>
       </c>
       <c r="B500" t="n">
-        <v>25429</v>
+        <v>19195</v>
       </c>
       <c r="C500" t="n">
-        <v>44.73</v>
+        <v>153.83</v>
       </c>
       <c r="D500" t="n">
-        <v>25154</v>
+        <v>21170</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>8.58</v>
+        <v>179.81</v>
       </c>
       <c r="B501" t="n">
-        <v>22734</v>
+        <v>19728</v>
       </c>
       <c r="C501" t="n">
-        <v>8.33</v>
+        <v>145.45</v>
       </c>
       <c r="D501" t="n">
-        <v>10803</v>
+        <v>21760</v>
       </c>
     </row>
   </sheetData>
